--- a/Relatorio_2024_12.xlsx
+++ b/Relatorio_2024_12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="556">
   <si>
     <t>CODIGO_ALTO</t>
   </si>
@@ -55,15 +55,6 @@
     <t>PONTOS</t>
   </si>
   <si>
-    <t>Base_Soma</t>
-  </si>
-  <si>
-    <t>Soma_Hierarquica</t>
-  </si>
-  <si>
-    <t>codigo_pai</t>
-  </si>
-  <si>
     <t>ITEM_KEY</t>
   </si>
   <si>
@@ -73,6 +64,15 @@
     <t>SOMA_N1</t>
   </si>
   <si>
+    <t>valor_base</t>
+  </si>
+  <si>
+    <t>SETOR</t>
+  </si>
+  <si>
+    <t>total_setor</t>
+  </si>
+  <si>
     <t>ESPCAR_A1S1R3</t>
   </si>
   <si>
@@ -1603,24 +1603,18 @@
     <t>R$ 2.816,00</t>
   </si>
   <si>
-    <t>R$ 360.679,14</t>
+    <t>R$ 360.679,13</t>
   </si>
   <si>
     <t>R$ 16.127,04</t>
   </si>
   <si>
-    <t>R$ 25.048,97</t>
-  </si>
-  <si>
     <t>R$ 712.670,02</t>
   </si>
   <si>
     <t>R$ 5.602,28</t>
   </si>
   <si>
-    <t>R$ 20.384,02</t>
-  </si>
-  <si>
     <t>R$ 328.804,83</t>
   </si>
   <si>
@@ -1633,7 +1627,7 @@
     <t>R$ 1.979,30</t>
   </si>
   <si>
-    <t>R$ 239.205,42</t>
+    <t>R$ 239.206,51</t>
   </si>
   <si>
     <t>R$ 7.538,98</t>
@@ -1642,7 +1636,7 @@
     <t>R$ 49.097,71</t>
   </si>
   <si>
-    <t>R$ 429.182,43</t>
+    <t>R$ 429.186,67</t>
   </si>
   <si>
     <t>R$ 7.816,00</t>
@@ -1666,10 +1660,10 @@
     <t>R$ 496.387,54</t>
   </si>
   <si>
-    <t>R$ 1.905.667,09</t>
-  </si>
-  <si>
-    <t>R$ 2.402.054,63</t>
+    <t>R$ 1.905.674,60</t>
+  </si>
+  <si>
+    <t>R$ 2.402.062,14</t>
   </si>
   <si>
     <t>01</t>
@@ -2115,28 +2109,25 @@
         <v>347</v>
       </c>
       <c r="K2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L2" s="1">
-        <v>0.2028539464882436</v>
+        <v>0.1504863717408673</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1546291.7712</v>
-      </c>
-      <c r="P2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>386572.9428</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
         <v>83</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>386572.9428</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2162,25 +2153,28 @@
         <v>406</v>
       </c>
       <c r="J3" s="1">
-        <v>0.0252650114292787</v>
+        <v>0.02526501448667866</v>
       </c>
       <c r="K3" t="s">
         <v>347</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
       </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>19533.542</v>
-      </c>
-      <c r="P3" t="s">
-        <v>552</v>
+        <v>1.01</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>9766.771000000001</v>
+      </c>
+      <c r="R3" t="s">
+        <v>550</v>
+      </c>
+      <c r="S3">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2206,22 +2200,25 @@
         <v>347</v>
       </c>
       <c r="J4" s="1">
-        <v>0.0252650114292787</v>
+        <v>0.02526501448667866</v>
       </c>
       <c r="K4" t="s">
         <v>347</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
       </c>
       <c r="M4">
         <v>2</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
+      <c r="Q4">
         <v>9766.771000000001</v>
       </c>
-      <c r="P4" t="s">
-        <v>552</v>
+      <c r="R4" t="s">
+        <v>550</v>
+      </c>
+      <c r="S4">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2253,25 +2250,28 @@
         <v>347</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0040335983156607</v>
+        <v>0.004033598390787324</v>
       </c>
       <c r="K5" t="s">
         <v>347</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
-      <c r="N5">
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
         <v>1559.28</v>
       </c>
-      <c r="O5">
-        <v>1559.28</v>
-      </c>
-      <c r="P5" t="s">
-        <v>84</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
+      <c r="R5" t="s">
+        <v>550</v>
+      </c>
+      <c r="S5">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2303,25 +2303,28 @@
         <v>347</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0050017208912315</v>
+        <v>0.005001708050220012</v>
       </c>
       <c r="K6" t="s">
         <v>347</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
       </c>
       <c r="M6">
         <v>3</v>
       </c>
-      <c r="N6">
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>1933.525</v>
       </c>
-      <c r="O6">
-        <v>1933.525</v>
-      </c>
-      <c r="P6" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
+      <c r="R6" t="s">
+        <v>550</v>
+      </c>
+      <c r="S6">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2353,25 +2356,28 @@
         <v>347</v>
       </c>
       <c r="J7" s="1">
-        <v>0.0048458382822698</v>
+        <v>0.004845843546192442</v>
       </c>
       <c r="K7" t="s">
         <v>347</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
       </c>
       <c r="M7">
         <v>3</v>
       </c>
-      <c r="N7">
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>1873.272</v>
       </c>
-      <c r="O7">
-        <v>1873.272</v>
-      </c>
-      <c r="P7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
+      <c r="R7" t="s">
+        <v>550</v>
+      </c>
+      <c r="S7">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2403,25 +2409,28 @@
         <v>347</v>
       </c>
       <c r="J8" s="1">
-        <v>0.0113838539401166</v>
+        <v>0.01138386449947888</v>
       </c>
       <c r="K8" t="s">
         <v>347</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
       </c>
       <c r="M8">
         <v>3</v>
       </c>
-      <c r="N8">
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <v>4400.694</v>
       </c>
-      <c r="O8">
-        <v>4400.694</v>
-      </c>
-      <c r="P8" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
+      <c r="R8" t="s">
+        <v>550</v>
+      </c>
+      <c r="S8">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2447,25 +2456,28 @@
         <v>529</v>
       </c>
       <c r="J9" s="1">
-        <v>0.9330170152878</v>
+        <v>0.9330170114533944</v>
       </c>
       <c r="K9" t="s">
         <v>347</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>721358.2636000001</v>
-      </c>
-      <c r="P9" t="s">
-        <v>552</v>
+        <v>1.02</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>360679.1318</v>
+      </c>
+      <c r="R9" t="s">
+        <v>550</v>
+      </c>
+      <c r="S9">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2491,22 +2503,25 @@
         <v>347</v>
       </c>
       <c r="J10" s="1">
-        <v>0.5720342305378583</v>
+        <v>0.5720342411921129</v>
       </c>
       <c r="K10" t="s">
         <v>347</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
       </c>
       <c r="M10">
         <v>2</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
+      <c r="Q10">
         <v>221132.96</v>
       </c>
-      <c r="P10" t="s">
-        <v>552</v>
+      <c r="R10" t="s">
+        <v>550</v>
+      </c>
+      <c r="S10">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2538,25 +2553,28 @@
         <v>347</v>
       </c>
       <c r="J11" s="1">
-        <v>0.5720342305378583</v>
+        <v>0.5720342411921129</v>
       </c>
       <c r="K11" t="s">
         <v>347</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
       </c>
       <c r="M11">
         <v>3</v>
       </c>
-      <c r="N11">
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
         <v>221132.96</v>
       </c>
-      <c r="O11">
-        <v>221132.96</v>
-      </c>
-      <c r="P11" t="s">
-        <v>90</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
+      <c r="R11" t="s">
+        <v>550</v>
+      </c>
+      <c r="S11">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2582,22 +2600,25 @@
         <v>347</v>
       </c>
       <c r="J12" s="1">
-        <v>0.3609827847499418</v>
+        <v>0.3609827702612818</v>
       </c>
       <c r="K12" t="s">
         <v>347</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
       </c>
       <c r="M12">
         <v>2</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
+      <c r="Q12">
         <v>139546.1718</v>
       </c>
-      <c r="P12" t="s">
-        <v>552</v>
+      <c r="R12" t="s">
+        <v>550</v>
+      </c>
+      <c r="S12">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2629,25 +2650,28 @@
         <v>347</v>
       </c>
       <c r="J13" s="1">
-        <v>0.0418025886187846</v>
+        <v>0.04180259457103422</v>
       </c>
       <c r="K13" t="s">
         <v>347</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
       </c>
       <c r="M13">
         <v>3</v>
       </c>
-      <c r="N13">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
         <v>16159.752</v>
       </c>
-      <c r="O13">
-        <v>16159.752</v>
-      </c>
-      <c r="P13" t="s">
-        <v>90</v>
-      </c>
-      <c r="R13">
-        <v>1</v>
+      <c r="R13" t="s">
+        <v>550</v>
+      </c>
+      <c r="S13">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2679,25 +2703,28 @@
         <v>347</v>
       </c>
       <c r="J14" s="1">
-        <v>0.0140806541171595</v>
+        <v>0.01408065437941458</v>
       </c>
       <c r="K14" t="s">
         <v>347</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
       </c>
       <c r="M14">
         <v>3</v>
       </c>
-      <c r="N14">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
         <v>5443.200000000001</v>
       </c>
-      <c r="O14">
-        <v>5443.200000000001</v>
-      </c>
-      <c r="P14" t="s">
-        <v>90</v>
-      </c>
-      <c r="R14">
-        <v>1</v>
+      <c r="R14" t="s">
+        <v>550</v>
+      </c>
+      <c r="S14">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2729,25 +2756,28 @@
         <v>347</v>
       </c>
       <c r="J15" s="1">
-        <v>0.0283373164107835</v>
+        <v>0.02833731693857184</v>
       </c>
       <c r="K15" t="s">
         <v>347</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
       </c>
       <c r="M15">
         <v>3</v>
       </c>
-      <c r="N15">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
         <v>10954.44</v>
       </c>
-      <c r="O15">
-        <v>10954.44</v>
-      </c>
-      <c r="P15" t="s">
-        <v>90</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
+      <c r="R15" t="s">
+        <v>550</v>
+      </c>
+      <c r="S15">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2779,25 +2809,28 @@
         <v>347</v>
       </c>
       <c r="J16" s="1">
-        <v>0.0259318713324354</v>
+        <v>0.02593187181542184</v>
       </c>
       <c r="K16" t="s">
         <v>347</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
       </c>
       <c r="M16">
         <v>3</v>
       </c>
-      <c r="N16">
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
         <v>10024.56</v>
       </c>
-      <c r="O16">
-        <v>10024.56</v>
-      </c>
-      <c r="P16" t="s">
-        <v>90</v>
-      </c>
-      <c r="R16">
-        <v>1</v>
+      <c r="R16" t="s">
+        <v>550</v>
+      </c>
+      <c r="S16">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2829,25 +2862,28 @@
         <v>347</v>
       </c>
       <c r="J17" s="1">
-        <v>0.003276354437112</v>
+        <v>0.003276359671802669</v>
       </c>
       <c r="K17" t="s">
         <v>347</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
       </c>
       <c r="M17">
         <v>3</v>
       </c>
-      <c r="N17">
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
         <v>1266.552</v>
       </c>
-      <c r="O17">
-        <v>1266.552</v>
-      </c>
-      <c r="P17" t="s">
-        <v>90</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
+      <c r="R17" t="s">
+        <v>550</v>
+      </c>
+      <c r="S17">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2879,25 +2915,28 @@
         <v>347</v>
       </c>
       <c r="J18" s="1">
-        <v>0.0029334954760802</v>
+        <v>0.002933502256485396</v>
       </c>
       <c r="K18" t="s">
         <v>347</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
       </c>
       <c r="M18">
         <v>3</v>
       </c>
-      <c r="N18">
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
         <v>1134.0126</v>
       </c>
-      <c r="O18">
-        <v>1134.0126</v>
-      </c>
-      <c r="P18" t="s">
-        <v>90</v>
-      </c>
-      <c r="R18">
-        <v>1</v>
+      <c r="R18" t="s">
+        <v>550</v>
+      </c>
+      <c r="S18">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2929,25 +2968,28 @@
         <v>347</v>
       </c>
       <c r="J19" s="1">
-        <v>0.0032663175216993</v>
+        <v>0.003266320686735865</v>
       </c>
       <c r="K19" t="s">
         <v>347</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
       </c>
       <c r="M19">
         <v>3</v>
       </c>
-      <c r="N19">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
         <v>1262.6712</v>
       </c>
-      <c r="O19">
-        <v>1262.6712</v>
-      </c>
-      <c r="P19" t="s">
-        <v>90</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
+      <c r="R19" t="s">
+        <v>550</v>
+      </c>
+      <c r="S19">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2979,25 +3021,28 @@
         <v>347</v>
       </c>
       <c r="J20" s="1">
-        <v>0.0845173465965479</v>
+        <v>0.08451733523653121</v>
       </c>
       <c r="K20" t="s">
         <v>347</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
       </c>
       <c r="M20">
         <v>3</v>
       </c>
-      <c r="N20">
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
         <v>32672.115</v>
       </c>
-      <c r="O20">
-        <v>32672.115</v>
-      </c>
-      <c r="P20" t="s">
-        <v>90</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
+      <c r="R20" t="s">
+        <v>550</v>
+      </c>
+      <c r="S20">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3029,25 +3074,28 @@
         <v>347</v>
       </c>
       <c r="J21" s="1">
-        <v>0.0036912825897414</v>
+        <v>0.003691282658492362</v>
       </c>
       <c r="K21" t="s">
         <v>347</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
       </c>
       <c r="M21">
         <v>3</v>
       </c>
-      <c r="N21">
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
         <v>1426.95</v>
       </c>
-      <c r="O21">
-        <v>1426.95</v>
-      </c>
-      <c r="P21" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21">
-        <v>1</v>
+      <c r="R21" t="s">
+        <v>550</v>
+      </c>
+      <c r="S21">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3079,25 +3127,28 @@
         <v>347</v>
       </c>
       <c r="J22" s="1">
-        <v>0.0173025815696623</v>
+        <v>0.01730258189192645</v>
       </c>
       <c r="K22" t="s">
         <v>347</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
       </c>
       <c r="M22">
         <v>3</v>
       </c>
-      <c r="N22">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
         <v>6688.71</v>
       </c>
-      <c r="O22">
-        <v>6688.71</v>
-      </c>
-      <c r="P22" t="s">
-        <v>90</v>
-      </c>
-      <c r="R22">
-        <v>1</v>
+      <c r="R22" t="s">
+        <v>550</v>
+      </c>
+      <c r="S22">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3129,25 +3180,28 @@
         <v>347</v>
       </c>
       <c r="J23" s="1">
-        <v>0.0074118998755603</v>
+        <v>0.007411900013608506</v>
       </c>
       <c r="K23" t="s">
         <v>347</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
       </c>
       <c r="M23">
         <v>3</v>
       </c>
-      <c r="N23">
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
         <v>2865.24</v>
       </c>
-      <c r="O23">
-        <v>2865.24</v>
-      </c>
-      <c r="P23" t="s">
-        <v>90</v>
-      </c>
-      <c r="R23">
-        <v>1</v>
+      <c r="R23" t="s">
+        <v>550</v>
+      </c>
+      <c r="S23">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3179,25 +3233,28 @@
         <v>347</v>
       </c>
       <c r="J24" s="1">
-        <v>0.0100181349988404</v>
+        <v>0.01001812483809459</v>
       </c>
       <c r="K24" t="s">
         <v>347</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
       </c>
       <c r="M24">
         <v>3</v>
       </c>
-      <c r="N24">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
         <v>3872.736</v>
       </c>
-      <c r="O24">
-        <v>3872.736</v>
-      </c>
-      <c r="P24" t="s">
-        <v>90</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
+      <c r="R24" t="s">
+        <v>550</v>
+      </c>
+      <c r="S24">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3229,25 +3286,28 @@
         <v>347</v>
       </c>
       <c r="J25" s="1">
-        <v>0.022714031077446</v>
+        <v>0.02271401856632994</v>
       </c>
       <c r="K25" t="s">
         <v>347</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
       </c>
       <c r="M25">
         <v>3</v>
       </c>
-      <c r="N25">
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
         <v>8780.625</v>
       </c>
-      <c r="O25">
-        <v>8780.625</v>
-      </c>
-      <c r="P25" t="s">
-        <v>90</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
+      <c r="R25" t="s">
+        <v>550</v>
+      </c>
+      <c r="S25">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3279,25 +3339,28 @@
         <v>347</v>
       </c>
       <c r="J26" s="1">
-        <v>0.0956989101280883</v>
+        <v>0.09569890673683229</v>
       </c>
       <c r="K26" t="s">
         <v>347</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
       </c>
       <c r="M26">
         <v>3</v>
       </c>
-      <c r="N26">
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
         <v>36994.608</v>
       </c>
-      <c r="O26">
-        <v>36994.608</v>
-      </c>
-      <c r="P26" t="s">
-        <v>90</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
+      <c r="R26" t="s">
+        <v>550</v>
+      </c>
+      <c r="S26">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -3323,25 +3386,28 @@
         <v>530</v>
       </c>
       <c r="J27" s="1">
-        <v>0.0417179732829211</v>
+        <v>0.04171797405992689</v>
       </c>
       <c r="K27" t="s">
         <v>347</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>32254.08</v>
-      </c>
-      <c r="P27" t="s">
-        <v>552</v>
+        <v>1.03</v>
       </c>
       <c r="Q27">
-        <v>1.03</v>
+        <v>16127.04</v>
+      </c>
+      <c r="R27" t="s">
+        <v>550</v>
+      </c>
+      <c r="S27">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -3367,22 +3433,25 @@
         <v>347</v>
       </c>
       <c r="J28" s="1">
-        <v>0.006322221976473</v>
+        <v>0.006322222094225681</v>
       </c>
       <c r="K28" t="s">
         <v>347</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
       </c>
       <c r="M28">
         <v>2</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
+      <c r="Q28">
         <v>2444</v>
       </c>
-      <c r="P28" t="s">
-        <v>552</v>
+      <c r="R28" t="s">
+        <v>550</v>
+      </c>
+      <c r="S28">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3414,25 +3483,28 @@
         <v>347</v>
       </c>
       <c r="J29" s="1">
-        <v>0.006322221976473</v>
+        <v>0.006322222094225681</v>
       </c>
       <c r="K29" t="s">
         <v>347</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
       </c>
       <c r="M29">
         <v>3</v>
       </c>
-      <c r="N29">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
         <v>2444</v>
       </c>
-      <c r="O29">
-        <v>2444</v>
-      </c>
-      <c r="P29" t="s">
-        <v>108</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
+      <c r="R29" t="s">
+        <v>550</v>
+      </c>
+      <c r="S29">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -3458,22 +3530,25 @@
         <v>347</v>
       </c>
       <c r="J30" s="1">
-        <v>0.0353957513064481</v>
+        <v>0.03539575196570121</v>
       </c>
       <c r="K30" t="s">
         <v>347</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
       </c>
       <c r="M30">
         <v>2</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
+      <c r="Q30">
         <v>13683.04</v>
       </c>
-      <c r="P30" t="s">
-        <v>552</v>
+      <c r="R30" t="s">
+        <v>550</v>
+      </c>
+      <c r="S30">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3505,25 +3580,28 @@
         <v>347</v>
       </c>
       <c r="J31" s="1">
-        <v>0.0353957513064481</v>
+        <v>0.03539575196570121</v>
       </c>
       <c r="K31" t="s">
         <v>347</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
       </c>
       <c r="M31">
         <v>3</v>
       </c>
-      <c r="N31">
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="Q31">
         <v>13683.04</v>
       </c>
-      <c r="O31">
-        <v>13683.04</v>
-      </c>
-      <c r="P31" t="s">
-        <v>108</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
+      <c r="R31" t="s">
+        <v>550</v>
+      </c>
+      <c r="S31">
+        <v>773145.8855999999</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -3549,31 +3627,28 @@
         <v>347</v>
       </c>
       <c r="K32" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L32" s="1">
-        <v>0.3900574345104934</v>
+        <v>0.2893629455449101</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>2973289.4508</v>
-      </c>
-      <c r="P32" t="s">
+        <v>2</v>
+      </c>
+      <c r="P32">
+        <v>743322.3627000001</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="s">
         <v>113</v>
       </c>
-      <c r="Q32">
-        <v>2</v>
-      </c>
-      <c r="S32">
-        <v>743322.3627000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3593,31 +3668,34 @@
         <v>347</v>
       </c>
       <c r="I33" t="s">
-        <v>531</v>
+        <v>429</v>
       </c>
       <c r="J33" s="1">
-        <v>0.0336987128055679</v>
+        <v>0.03370012763911697</v>
       </c>
       <c r="K33" t="s">
         <v>347</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
       </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>50100.11699999999</v>
-      </c>
-      <c r="P33" t="s">
-        <v>553</v>
+        <v>2.01</v>
       </c>
       <c r="Q33">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+        <v>25050.0585</v>
+      </c>
+      <c r="R33" t="s">
+        <v>551</v>
+      </c>
+      <c r="S33">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -3640,25 +3718,28 @@
         <v>347</v>
       </c>
       <c r="J34" s="1">
-        <v>0.0336987128055679</v>
+        <v>0.03370012763911697</v>
       </c>
       <c r="K34" t="s">
         <v>347</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
       </c>
       <c r="M34">
         <v>2</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
+      <c r="Q34">
         <v>25050.0585</v>
       </c>
-      <c r="P34" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="R34" t="s">
+        <v>551</v>
+      </c>
+      <c r="S34">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -3687,28 +3768,31 @@
         <v>347</v>
       </c>
       <c r="J35" s="1">
-        <v>0.0053798272179134</v>
+        <v>0.005379819309450732</v>
       </c>
       <c r="K35" t="s">
         <v>347</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
       </c>
       <c r="M35">
         <v>3</v>
       </c>
-      <c r="N35">
+      <c r="O35">
+        <v>2</v>
+      </c>
+      <c r="Q35">
         <v>3998.94</v>
       </c>
-      <c r="O35">
-        <v>3998.94</v>
-      </c>
-      <c r="P35" t="s">
-        <v>114</v>
-      </c>
-      <c r="R35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="R35" t="s">
+        <v>551</v>
+      </c>
+      <c r="S35">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -3737,28 +3821,31 @@
         <v>347</v>
       </c>
       <c r="J36" s="1">
-        <v>0.0066710454821237</v>
+        <v>0.006672498701618842</v>
       </c>
       <c r="K36" t="s">
         <v>347</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
       </c>
       <c r="M36">
         <v>3</v>
       </c>
-      <c r="N36">
+      <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="Q36">
         <v>4959.817499999999</v>
       </c>
-      <c r="O36">
-        <v>4959.817499999999</v>
-      </c>
-      <c r="P36" t="s">
-        <v>114</v>
-      </c>
-      <c r="R36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="R36" t="s">
+        <v>551</v>
+      </c>
+      <c r="S36">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -3787,28 +3874,31 @@
         <v>347</v>
       </c>
       <c r="J37" s="1">
-        <v>0.0064631676690753</v>
+        <v>0.006463152786833275</v>
       </c>
       <c r="K37" t="s">
         <v>347</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
       </c>
       <c r="M37">
         <v>3</v>
       </c>
-      <c r="N37">
+      <c r="O37">
+        <v>2</v>
+      </c>
+      <c r="Q37">
         <v>4804.205999999999</v>
       </c>
-      <c r="O37">
-        <v>4804.205999999999</v>
-      </c>
-      <c r="P37" t="s">
-        <v>114</v>
-      </c>
-      <c r="R37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="R37" t="s">
+        <v>551</v>
+      </c>
+      <c r="S37">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -3837,28 +3927,31 @@
         <v>347</v>
       </c>
       <c r="J38" s="1">
-        <v>0.0151846724364553</v>
+        <v>0.01518465684121412</v>
       </c>
       <c r="K38" t="s">
         <v>347</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
       </c>
       <c r="M38">
         <v>3</v>
       </c>
-      <c r="N38">
+      <c r="O38">
+        <v>2</v>
+      </c>
+      <c r="Q38">
         <v>11287.095</v>
       </c>
-      <c r="O38">
-        <v>11287.095</v>
-      </c>
-      <c r="P38" t="s">
-        <v>114</v>
-      </c>
-      <c r="R38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="R38" t="s">
+        <v>551</v>
+      </c>
+      <c r="S38">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -3878,31 +3971,34 @@
         <v>347</v>
       </c>
       <c r="I39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J39" s="1">
-        <v>0.958764465330045</v>
+        <v>0.958763058885165</v>
       </c>
       <c r="K39" t="s">
         <v>347</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>1425340.0444</v>
-      </c>
-      <c r="P39" t="s">
-        <v>553</v>
+        <v>2.02</v>
       </c>
       <c r="Q39">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+        <v>712670.0222</v>
+      </c>
+      <c r="R39" t="s">
+        <v>551</v>
+      </c>
+      <c r="S39">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -3925,25 +4021,28 @@
         <v>347</v>
       </c>
       <c r="J40" s="1">
-        <v>0.8995866888081919</v>
+        <v>0.8995853663962424</v>
       </c>
       <c r="K40" t="s">
         <v>347</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
       </c>
       <c r="M40">
         <v>2</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
+      <c r="Q40">
         <v>668681.92</v>
       </c>
-      <c r="P40" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="R40" t="s">
+        <v>551</v>
+      </c>
+      <c r="S40">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -3972,28 +4071,31 @@
         <v>347</v>
       </c>
       <c r="J41" s="1">
-        <v>0.8995866888081919</v>
+        <v>0.8995853663962424</v>
       </c>
       <c r="K41" t="s">
         <v>347</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
       </c>
       <c r="M41">
         <v>3</v>
       </c>
-      <c r="N41">
+      <c r="O41">
+        <v>2</v>
+      </c>
+      <c r="Q41">
         <v>668681.92</v>
       </c>
-      <c r="O41">
-        <v>668681.92</v>
-      </c>
-      <c r="P41" t="s">
-        <v>120</v>
-      </c>
-      <c r="R41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="R41" t="s">
+        <v>551</v>
+      </c>
+      <c r="S41">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -4016,25 +4118,28 @@
         <v>347</v>
       </c>
       <c r="J42" s="1">
-        <v>0.059177776521853</v>
+        <v>0.05917769248892261</v>
       </c>
       <c r="K42" t="s">
         <v>347</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
       </c>
       <c r="M42">
         <v>2</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>43988.10220000001</v>
-      </c>
-      <c r="P42" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="Q42">
+        <v>43988.10219999999</v>
+      </c>
+      <c r="R42" t="s">
+        <v>551</v>
+      </c>
+      <c r="S42">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -4063,28 +4168,31 @@
         <v>347</v>
       </c>
       <c r="J43" s="1">
-        <v>0.0093171153302259</v>
+        <v>0.009317098943241574</v>
       </c>
       <c r="K43" t="s">
         <v>347</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
       </c>
       <c r="M43">
         <v>3</v>
       </c>
-      <c r="N43">
+      <c r="O43">
+        <v>2</v>
+      </c>
+      <c r="Q43">
         <v>6925.608</v>
       </c>
-      <c r="O43">
-        <v>6925.608</v>
-      </c>
-      <c r="P43" t="s">
-        <v>120</v>
-      </c>
-      <c r="R43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="R43" t="s">
+        <v>551</v>
+      </c>
+      <c r="S43">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -4113,28 +4221,31 @@
         <v>347</v>
       </c>
       <c r="J44" s="1">
-        <v>0.0031383468954144</v>
+        <v>0.003138342281976391</v>
       </c>
       <c r="K44" t="s">
         <v>347</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
       </c>
       <c r="M44">
         <v>3</v>
       </c>
-      <c r="N44">
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="Q44">
         <v>2332.8</v>
       </c>
-      <c r="O44">
-        <v>2332.8</v>
-      </c>
-      <c r="P44" t="s">
-        <v>120</v>
-      </c>
-      <c r="R44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="R44" t="s">
+        <v>551</v>
+      </c>
+      <c r="S44">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -4163,28 +4274,31 @@
         <v>347</v>
       </c>
       <c r="J45" s="1">
-        <v>0.0063159231270215</v>
+        <v>0.006315913842477486</v>
       </c>
       <c r="K45" t="s">
         <v>347</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
       </c>
       <c r="M45">
         <v>3</v>
       </c>
-      <c r="N45">
+      <c r="O45">
+        <v>2</v>
+      </c>
+      <c r="Q45">
         <v>4694.76</v>
       </c>
-      <c r="O45">
-        <v>4694.76</v>
-      </c>
-      <c r="P45" t="s">
-        <v>120</v>
-      </c>
-      <c r="R45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="R45" t="s">
+        <v>551</v>
+      </c>
+      <c r="S45">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -4213,28 +4327,31 @@
         <v>347</v>
       </c>
       <c r="J46" s="1">
-        <v>0.0057797888657215</v>
+        <v>0.005779780369306519</v>
       </c>
       <c r="K46" t="s">
         <v>347</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
       </c>
       <c r="M46">
         <v>3</v>
       </c>
-      <c r="N46">
+      <c r="O46">
+        <v>2</v>
+      </c>
+      <c r="Q46">
         <v>4296.24</v>
       </c>
-      <c r="O46">
-        <v>4296.24</v>
-      </c>
-      <c r="P46" t="s">
-        <v>120</v>
-      </c>
-      <c r="R46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="R46" t="s">
+        <v>551</v>
+      </c>
+      <c r="S46">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -4263,28 +4380,31 @@
         <v>347</v>
       </c>
       <c r="J47" s="1">
-        <v>0.0007302495191614</v>
+        <v>0.0007302457550561731</v>
       </c>
       <c r="K47" t="s">
         <v>347</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
       </c>
       <c r="M47">
         <v>3</v>
       </c>
-      <c r="N47">
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="Q47">
         <v>542.808</v>
       </c>
-      <c r="O47">
-        <v>542.808</v>
-      </c>
-      <c r="P47" t="s">
-        <v>120</v>
-      </c>
-      <c r="R47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="R47" t="s">
+        <v>551</v>
+      </c>
+      <c r="S47">
+        <v>1486644.7254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -4313,25 +4433,28 @@
         <v>347</v>
       </c>
       <c r="J48" s="1">
-        <v>0.0006538357230111</v>
+        <v>0.0006538285734262896</v>
       </c>
       <c r="K48" t="s">
         <v>347</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
       </c>
       <c r="M48">
         <v>3</v>
       </c>
-      <c r="N48">
+      <c r="O48">
+        <v>2</v>
+      </c>
+      <c r="Q48">
         <v>486.0054</v>
       </c>
-      <c r="O48">
-        <v>486.0054</v>
-      </c>
-      <c r="P48" t="s">
-        <v>120</v>
-      </c>
-      <c r="R48">
-        <v>2</v>
+      <c r="R48" t="s">
+        <v>551</v>
+      </c>
+      <c r="S48">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -4363,25 +4486,28 @@
         <v>347</v>
       </c>
       <c r="J49" s="1">
-        <v>0.0007280028459295</v>
+        <v>0.0007280082332440233</v>
       </c>
       <c r="K49" t="s">
         <v>347</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
       </c>
       <c r="M49">
         <v>3</v>
       </c>
-      <c r="N49">
+      <c r="O49">
+        <v>2</v>
+      </c>
+      <c r="Q49">
         <v>541.1448</v>
       </c>
-      <c r="O49">
-        <v>541.1448</v>
-      </c>
-      <c r="P49" t="s">
-        <v>120</v>
-      </c>
-      <c r="R49">
-        <v>2</v>
+      <c r="R49" t="s">
+        <v>551</v>
+      </c>
+      <c r="S49">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -4413,25 +4539,28 @@
         <v>347</v>
       </c>
       <c r="J50" s="1">
-        <v>0.0188375209551046</v>
+        <v>0.01883749999009683</v>
       </c>
       <c r="K50" t="s">
         <v>347</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
       </c>
       <c r="M50">
         <v>3</v>
       </c>
-      <c r="N50">
+      <c r="O50">
+        <v>2</v>
+      </c>
+      <c r="Q50">
         <v>14002.335</v>
       </c>
-      <c r="O50">
-        <v>14002.335</v>
-      </c>
-      <c r="P50" t="s">
-        <v>120</v>
-      </c>
-      <c r="R50">
-        <v>2</v>
+      <c r="R50" t="s">
+        <v>551</v>
+      </c>
+      <c r="S50">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -4463,25 +4592,28 @@
         <v>347</v>
       </c>
       <c r="J51" s="1">
-        <v>0.0008227263562631</v>
+        <v>0.0008227251468375606</v>
       </c>
       <c r="K51" t="s">
         <v>347</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
-      <c r="N51">
+      <c r="O51">
+        <v>2</v>
+      </c>
+      <c r="Q51">
         <v>611.55</v>
       </c>
-      <c r="O51">
-        <v>611.55</v>
-      </c>
-      <c r="P51" t="s">
-        <v>120</v>
-      </c>
-      <c r="R51">
-        <v>2</v>
+      <c r="R51" t="s">
+        <v>551</v>
+      </c>
+      <c r="S51">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -4513,25 +4645,28 @@
         <v>347</v>
       </c>
       <c r="J52" s="1">
-        <v>0.003856461688497</v>
+        <v>0.003856456019414738</v>
       </c>
       <c r="K52" t="s">
         <v>347</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0</v>
       </c>
       <c r="M52">
         <v>3</v>
       </c>
-      <c r="N52">
+      <c r="O52">
+        <v>2</v>
+      </c>
+      <c r="Q52">
         <v>2866.59</v>
       </c>
-      <c r="O52">
-        <v>2866.59</v>
-      </c>
-      <c r="P52" t="s">
-        <v>120</v>
-      </c>
-      <c r="R52">
-        <v>2</v>
+      <c r="R52" t="s">
+        <v>551</v>
+      </c>
+      <c r="S52">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -4563,25 +4698,28 @@
         <v>347</v>
       </c>
       <c r="J53" s="1">
-        <v>0.0001223696989055</v>
+        <v>0.0001223695190194498</v>
       </c>
       <c r="K53" t="s">
         <v>347</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
       </c>
       <c r="M53">
         <v>3</v>
       </c>
-      <c r="N53">
+      <c r="O53">
+        <v>2</v>
+      </c>
+      <c r="Q53">
         <v>90.96000000000001</v>
       </c>
-      <c r="O53">
-        <v>90.96000000000001</v>
-      </c>
-      <c r="P53" t="s">
-        <v>120</v>
-      </c>
-      <c r="R53">
-        <v>2</v>
+      <c r="R53" t="s">
+        <v>551</v>
+      </c>
+      <c r="S53">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -4613,25 +4751,28 @@
         <v>347</v>
       </c>
       <c r="J54" s="1">
-        <v>0.002232870317299</v>
+        <v>0.002232872416176536</v>
       </c>
       <c r="K54" t="s">
         <v>347</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
       </c>
       <c r="M54">
         <v>3</v>
       </c>
-      <c r="N54">
+      <c r="O54">
+        <v>2</v>
+      </c>
+      <c r="Q54">
         <v>1659.744</v>
       </c>
-      <c r="O54">
-        <v>1659.744</v>
-      </c>
-      <c r="P54" t="s">
-        <v>120</v>
-      </c>
-      <c r="R54">
-        <v>2</v>
+      <c r="R54" t="s">
+        <v>551</v>
+      </c>
+      <c r="S54">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -4663,25 +4804,28 @@
         <v>347</v>
       </c>
       <c r="J55" s="1">
-        <v>0.0050625888856913</v>
+        <v>0.005062574717019206</v>
       </c>
       <c r="K55" t="s">
         <v>347</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
       </c>
       <c r="M55">
         <v>3</v>
       </c>
-      <c r="N55">
+      <c r="O55">
+        <v>2</v>
+      </c>
+      <c r="Q55">
         <v>3763.125</v>
       </c>
-      <c r="O55">
-        <v>3763.125</v>
-      </c>
-      <c r="P55" t="s">
-        <v>120</v>
-      </c>
-      <c r="R55">
-        <v>2</v>
+      <c r="R55" t="s">
+        <v>551</v>
+      </c>
+      <c r="S55">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4713,25 +4857,28 @@
         <v>347</v>
       </c>
       <c r="J56" s="1">
-        <v>0.0015799763136066</v>
+        <v>0.001579976681629842</v>
       </c>
       <c r="K56" t="s">
         <v>347</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
       </c>
       <c r="M56">
         <v>3</v>
       </c>
-      <c r="N56">
+      <c r="O56">
+        <v>2</v>
+      </c>
+      <c r="Q56">
         <v>1174.432</v>
       </c>
-      <c r="O56">
-        <v>1174.432</v>
-      </c>
-      <c r="P56" t="s">
-        <v>120</v>
-      </c>
-      <c r="R56">
-        <v>2</v>
+      <c r="R56" t="s">
+        <v>551</v>
+      </c>
+      <c r="S56">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4754,28 +4901,31 @@
         <v>347</v>
       </c>
       <c r="I57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0075368218643871</v>
+        <v>0.007536813475718131</v>
       </c>
       <c r="K57" t="s">
         <v>347</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>11204.564</v>
-      </c>
-      <c r="P57" t="s">
-        <v>553</v>
+        <v>2.03</v>
       </c>
       <c r="Q57">
-        <v>2.03</v>
+        <v>5602.282</v>
+      </c>
+      <c r="R57" t="s">
+        <v>551</v>
+      </c>
+      <c r="S57">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4801,22 +4951,25 @@
         <v>347</v>
       </c>
       <c r="J58" s="1">
-        <v>0.0043154287781916</v>
+        <v>0.004315422434417767</v>
       </c>
       <c r="K58" t="s">
         <v>347</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
       </c>
       <c r="M58">
         <v>2</v>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
+      <c r="Q58">
         <v>3207.75</v>
       </c>
-      <c r="P58" t="s">
-        <v>553</v>
+      <c r="R58" t="s">
+        <v>551</v>
+      </c>
+      <c r="S58">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4848,25 +5001,28 @@
         <v>347</v>
       </c>
       <c r="J59" s="1">
-        <v>0.0043154287781916</v>
+        <v>0.004315422434417767</v>
       </c>
       <c r="K59" t="s">
         <v>347</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
       </c>
       <c r="M59">
         <v>3</v>
       </c>
-      <c r="N59">
+      <c r="O59">
+        <v>2</v>
+      </c>
+      <c r="Q59">
         <v>3207.75</v>
       </c>
-      <c r="O59">
-        <v>3207.75</v>
-      </c>
-      <c r="P59" t="s">
-        <v>138</v>
-      </c>
-      <c r="R59">
-        <v>2</v>
+      <c r="R59" t="s">
+        <v>551</v>
+      </c>
+      <c r="S59">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4892,22 +5048,25 @@
         <v>347</v>
       </c>
       <c r="J60" s="1">
-        <v>0.0032213930861954</v>
+        <v>0.003221391041300365</v>
       </c>
       <c r="K60" t="s">
         <v>347</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
       </c>
       <c r="M60">
         <v>2</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
+      <c r="Q60">
         <v>2394.532</v>
       </c>
-      <c r="P60" t="s">
-        <v>553</v>
+      <c r="R60" t="s">
+        <v>551</v>
+      </c>
+      <c r="S60">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4939,25 +5098,28 @@
         <v>347</v>
       </c>
       <c r="J61" s="1">
-        <v>0.0032213930861954</v>
+        <v>0.003221391041300365</v>
       </c>
       <c r="K61" t="s">
         <v>347</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
       </c>
       <c r="M61">
         <v>3</v>
       </c>
-      <c r="N61">
+      <c r="O61">
+        <v>2</v>
+      </c>
+      <c r="Q61">
         <v>2394.532</v>
       </c>
-      <c r="O61">
-        <v>2394.532</v>
-      </c>
-      <c r="P61" t="s">
-        <v>138</v>
-      </c>
-      <c r="R61">
-        <v>2</v>
+      <c r="R61" t="s">
+        <v>551</v>
+      </c>
+      <c r="S61">
+        <v>1486644.7254</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4983,28 +5145,25 @@
         <v>347</v>
       </c>
       <c r="K62" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L62" s="1">
-        <v>0.1877248161150642</v>
+        <v>0.1392633141006688</v>
       </c>
       <c r="M62">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>1430971.55</v>
-      </c>
-      <c r="P62" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62">
+        <v>357742.8875</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62" t="s">
         <v>143</v>
-      </c>
-      <c r="Q62">
-        <v>3</v>
-      </c>
-      <c r="S62">
-        <v>357742.8875</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -5027,28 +5186,31 @@
         <v>347</v>
       </c>
       <c r="I63" t="s">
-        <v>534</v>
+        <v>452</v>
       </c>
       <c r="J63" s="1">
-        <v>0.0569796987659815</v>
+        <v>0.05698255985592445</v>
       </c>
       <c r="K63" t="s">
         <v>347</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>40770.211</v>
-      </c>
-      <c r="P63" t="s">
-        <v>554</v>
+        <v>3.01</v>
       </c>
       <c r="Q63">
-        <v>3.01</v>
+        <v>20385.1055</v>
+      </c>
+      <c r="R63" t="s">
+        <v>552</v>
+      </c>
+      <c r="S63">
+        <v>715485.775</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -5074,25 +5236,28 @@
         <v>347</v>
       </c>
       <c r="J64" s="1">
-        <v>0.0569796987659815</v>
+        <v>0.05698255985592445</v>
       </c>
       <c r="K64" t="s">
         <v>347</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
       </c>
       <c r="M64">
         <v>2</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
+      <c r="Q64">
         <v>20385.1055</v>
       </c>
-      <c r="P64" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18">
+      <c r="R64" t="s">
+        <v>552</v>
+      </c>
+      <c r="S64">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" t="s">
         <v>21</v>
       </c>
@@ -5121,28 +5286,31 @@
         <v>347</v>
       </c>
       <c r="J65" s="1">
-        <v>0.0090968961412952</v>
+        <v>0.009096868487706831</v>
       </c>
       <c r="K65" t="s">
         <v>347</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
       </c>
       <c r="M65">
         <v>3</v>
       </c>
-      <c r="N65">
+      <c r="O65">
+        <v>3</v>
+      </c>
+      <c r="Q65">
         <v>3254.34</v>
       </c>
-      <c r="O65">
-        <v>3254.34</v>
-      </c>
-      <c r="P65" t="s">
-        <v>144</v>
-      </c>
-      <c r="R65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18">
+      <c r="R65" t="s">
+        <v>552</v>
+      </c>
+      <c r="S65">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
         <v>21</v>
       </c>
@@ -5171,28 +5339,31 @@
         <v>347</v>
       </c>
       <c r="J66" s="1">
-        <v>0.0112802585551926</v>
+        <v>0.01128325716887942</v>
       </c>
       <c r="K66" t="s">
         <v>347</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
       </c>
       <c r="M66">
         <v>3</v>
       </c>
-      <c r="N66">
+      <c r="O66">
+        <v>3</v>
+      </c>
+      <c r="Q66">
         <v>4036.505</v>
       </c>
-      <c r="O66">
-        <v>4036.505</v>
-      </c>
-      <c r="P66" t="s">
-        <v>144</v>
-      </c>
-      <c r="R66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18">
+      <c r="R66" t="s">
+        <v>552</v>
+      </c>
+      <c r="S66">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -5221,28 +5392,31 @@
         <v>347</v>
       </c>
       <c r="J67" s="1">
-        <v>0.0109287480523662</v>
+        <v>0.01092870364892999</v>
       </c>
       <c r="K67" t="s">
         <v>347</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
       </c>
       <c r="M67">
         <v>3</v>
       </c>
-      <c r="N67">
+      <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="Q67">
         <v>3909.666</v>
       </c>
-      <c r="O67">
-        <v>3909.666</v>
-      </c>
-      <c r="P67" t="s">
-        <v>144</v>
-      </c>
-      <c r="R67">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18">
+      <c r="R67" t="s">
+        <v>552</v>
+      </c>
+      <c r="S67">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -5271,28 +5445,31 @@
         <v>347</v>
       </c>
       <c r="J68" s="1">
-        <v>0.0256737960171274</v>
+        <v>0.02567373055040821</v>
       </c>
       <c r="K68" t="s">
         <v>347</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
       </c>
       <c r="M68">
         <v>3</v>
       </c>
-      <c r="N68">
+      <c r="O68">
+        <v>3</v>
+      </c>
+      <c r="Q68">
         <v>9184.594499999999</v>
       </c>
-      <c r="O68">
-        <v>9184.594499999999</v>
-      </c>
-      <c r="P68" t="s">
-        <v>144</v>
-      </c>
-      <c r="R68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18">
+      <c r="R68" t="s">
+        <v>552</v>
+      </c>
+      <c r="S68">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -5312,31 +5489,34 @@
         <v>347</v>
       </c>
       <c r="I69" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="J69" s="1">
-        <v>0.9191121361831354</v>
+        <v>0.9191093477714494</v>
       </c>
       <c r="K69" t="s">
         <v>347</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>657609.6639999999</v>
-      </c>
-      <c r="P69" t="s">
-        <v>554</v>
+        <v>3.02</v>
       </c>
       <c r="Q69">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18">
+        <v>328804.832</v>
+      </c>
+      <c r="R69" t="s">
+        <v>552</v>
+      </c>
+      <c r="S69">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -5359,25 +5539,28 @@
         <v>347</v>
       </c>
       <c r="J70" s="1">
-        <v>0.7573743968415209</v>
+        <v>0.7573720945046042</v>
       </c>
       <c r="K70" t="s">
         <v>347</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
+      <c r="Q70">
         <v>270944.48</v>
       </c>
-      <c r="P70" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18">
+      <c r="R70" t="s">
+        <v>552</v>
+      </c>
+      <c r="S70">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -5406,28 +5589,31 @@
         <v>347</v>
       </c>
       <c r="J71" s="1">
-        <v>0.7573743968415209</v>
+        <v>0.7573720945046042</v>
       </c>
       <c r="K71" t="s">
         <v>347</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
       </c>
       <c r="M71">
         <v>3</v>
       </c>
-      <c r="N71">
+      <c r="O71">
+        <v>3</v>
+      </c>
+      <c r="Q71">
         <v>270944.48</v>
       </c>
-      <c r="O71">
-        <v>270944.48</v>
-      </c>
-      <c r="P71" t="s">
-        <v>150</v>
-      </c>
-      <c r="R71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18">
+      <c r="R71" t="s">
+        <v>552</v>
+      </c>
+      <c r="S71">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -5450,25 +5636,28 @@
         <v>347</v>
       </c>
       <c r="J72" s="1">
-        <v>0.1617377393416145</v>
+        <v>0.1617372532668452</v>
       </c>
       <c r="K72" t="s">
         <v>347</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
       </c>
       <c r="M72">
         <v>2</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
+      <c r="Q72">
         <v>57860.352</v>
       </c>
-      <c r="P72" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18">
+      <c r="R72" t="s">
+        <v>552</v>
+      </c>
+      <c r="S72">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -5497,28 +5686,31 @@
         <v>347</v>
       </c>
       <c r="J73" s="1">
-        <v>0.152347642908936</v>
+        <v>0.1523471797884451</v>
       </c>
       <c r="K73" t="s">
         <v>347</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
       </c>
       <c r="M73">
         <v>3</v>
       </c>
-      <c r="N73">
+      <c r="O73">
+        <v>3</v>
+      </c>
+      <c r="Q73">
         <v>54501.12</v>
       </c>
-      <c r="O73">
-        <v>54501.12</v>
-      </c>
-      <c r="P73" t="s">
-        <v>150</v>
-      </c>
-      <c r="R73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18">
+      <c r="R73" t="s">
+        <v>552</v>
+      </c>
+      <c r="S73">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -5547,28 +5739,31 @@
         <v>347</v>
       </c>
       <c r="J74" s="1">
-        <v>0.00337799496732</v>
+        <v>0.003377979107970386</v>
       </c>
       <c r="K74" t="s">
         <v>347</v>
+      </c>
+      <c r="L74" s="1">
+        <v>0</v>
       </c>
       <c r="M74">
         <v>3</v>
       </c>
-      <c r="N74">
+      <c r="O74">
+        <v>3</v>
+      </c>
+      <c r="Q74">
         <v>1208.448</v>
       </c>
-      <c r="O74">
-        <v>1208.448</v>
-      </c>
-      <c r="P74" t="s">
-        <v>150</v>
-      </c>
-      <c r="R74">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18">
+      <c r="R74" t="s">
+        <v>552</v>
+      </c>
+      <c r="S74">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -5597,28 +5792,31 @@
         <v>347</v>
       </c>
       <c r="J75" s="1">
-        <v>0.0060121014653585</v>
+        <v>0.006012094370429657</v>
       </c>
       <c r="K75" t="s">
         <v>347</v>
+      </c>
+      <c r="L75" s="1">
+        <v>0</v>
       </c>
       <c r="M75">
         <v>3</v>
       </c>
-      <c r="N75">
+      <c r="O75">
+        <v>3</v>
+      </c>
+      <c r="Q75">
         <v>2150.784</v>
       </c>
-      <c r="O75">
-        <v>2150.784</v>
-      </c>
-      <c r="P75" t="s">
-        <v>150</v>
-      </c>
-      <c r="R75">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18">
+      <c r="R75" t="s">
+        <v>552</v>
+      </c>
+      <c r="S75">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -5638,31 +5836,34 @@
         <v>347</v>
       </c>
       <c r="I76" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J76" s="1">
-        <v>0.023908165050883</v>
+        <v>0.02390809237262614</v>
       </c>
       <c r="K76" t="s">
         <v>347</v>
+      </c>
+      <c r="L76" s="1">
+        <v>0</v>
       </c>
       <c r="M76">
         <v>1</v>
       </c>
       <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>17105.9</v>
-      </c>
-      <c r="P76" t="s">
-        <v>554</v>
+        <v>3.03</v>
       </c>
       <c r="Q76">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18">
+        <v>8552.950000000001</v>
+      </c>
+      <c r="R76" t="s">
+        <v>552</v>
+      </c>
+      <c r="S76">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -5685,25 +5886,28 @@
         <v>347</v>
       </c>
       <c r="J77" s="1">
-        <v>0.0119555500643201</v>
+        <v>0.01195551372073051</v>
       </c>
       <c r="K77" t="s">
         <v>347</v>
+      </c>
+      <c r="L77" s="1">
+        <v>0</v>
       </c>
       <c r="M77">
         <v>2</v>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
+      <c r="Q77">
         <v>4277</v>
       </c>
-      <c r="P77" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18">
+      <c r="R77" t="s">
+        <v>552</v>
+      </c>
+      <c r="S77">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -5732,28 +5936,31 @@
         <v>347</v>
       </c>
       <c r="J78" s="1">
-        <v>0.0119555500643201</v>
+        <v>0.01195551372073051</v>
       </c>
       <c r="K78" t="s">
         <v>347</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
-      <c r="N78">
+      <c r="O78">
+        <v>3</v>
+      </c>
+      <c r="Q78">
         <v>4277</v>
       </c>
-      <c r="O78">
-        <v>4277</v>
-      </c>
-      <c r="P78" t="s">
-        <v>157</v>
-      </c>
-      <c r="R78">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18">
+      <c r="R78" t="s">
+        <v>552</v>
+      </c>
+      <c r="S78">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -5776,25 +5983,28 @@
         <v>347</v>
       </c>
       <c r="J79" s="1">
-        <v>0.0119526149865629</v>
+        <v>0.01195257865189563</v>
       </c>
       <c r="K79" t="s">
         <v>347</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
       </c>
       <c r="M79">
         <v>2</v>
       </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
+      <c r="Q79">
         <v>4275.950000000001</v>
       </c>
-      <c r="P79" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18">
+      <c r="R79" t="s">
+        <v>552</v>
+      </c>
+      <c r="S79">
+        <v>715485.775</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -5823,25 +6033,28 @@
         <v>347</v>
       </c>
       <c r="J80" s="1">
-        <v>0.0119526149865629</v>
+        <v>0.01195257865189563</v>
       </c>
       <c r="K80" t="s">
         <v>347</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
       </c>
       <c r="M80">
         <v>3</v>
       </c>
-      <c r="N80">
+      <c r="O80">
+        <v>3</v>
+      </c>
+      <c r="Q80">
         <v>4275.950000000001</v>
       </c>
-      <c r="O80">
-        <v>4275.950000000001</v>
-      </c>
-      <c r="P80" t="s">
-        <v>157</v>
-      </c>
-      <c r="R80">
-        <v>3</v>
+      <c r="R80" t="s">
+        <v>552</v>
+      </c>
+      <c r="S80">
+        <v>715485.775</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5867,28 +6080,25 @@
         <v>347</v>
       </c>
       <c r="K81" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L81" s="1">
-        <v>0.0898848124036163</v>
+        <v>0.1315981249764736</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>1352209.4752</v>
-      </c>
-      <c r="P81" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81">
+        <v>338052.3688</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81" t="s">
         <v>162</v>
-      </c>
-      <c r="Q81">
-        <v>4</v>
-      </c>
-      <c r="S81">
-        <v>338052.3688</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -5914,25 +6124,28 @@
         <v>464</v>
       </c>
       <c r="J82" s="1">
-        <v>0.0096099086635712</v>
+        <v>0.009609879310766404</v>
       </c>
       <c r="K82" t="s">
         <v>347</v>
+      </c>
+      <c r="L82" s="1">
+        <v>0</v>
       </c>
       <c r="M82">
         <v>1</v>
       </c>
       <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>3292.17</v>
-      </c>
-      <c r="P82" t="s">
-        <v>555</v>
+        <v>4.01</v>
       </c>
       <c r="Q82">
-        <v>4.01</v>
+        <v>1646.085</v>
+      </c>
+      <c r="R82" t="s">
+        <v>553</v>
+      </c>
+      <c r="S82">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -5958,22 +6171,25 @@
         <v>347</v>
       </c>
       <c r="J83" s="1">
-        <v>0.0096099086635712</v>
+        <v>0.009609879310766404</v>
       </c>
       <c r="K83" t="s">
         <v>347</v>
+      </c>
+      <c r="L83" s="1">
+        <v>0</v>
       </c>
       <c r="M83">
         <v>2</v>
       </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
+      <c r="Q83">
         <v>1646.085</v>
       </c>
-      <c r="P83" t="s">
-        <v>555</v>
+      <c r="R83" t="s">
+        <v>553</v>
+      </c>
+      <c r="S83">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -6005,25 +6221,28 @@
         <v>347</v>
       </c>
       <c r="J84" s="1">
-        <v>0.0015342320266732</v>
+        <v>0.00153423200069827</v>
       </c>
       <c r="K84" t="s">
         <v>347</v>
+      </c>
+      <c r="L84" s="1">
+        <v>0</v>
       </c>
       <c r="M84">
         <v>3</v>
       </c>
-      <c r="N84">
+      <c r="O84">
+        <v>4</v>
+      </c>
+      <c r="Q84">
         <v>262.8</v>
       </c>
-      <c r="O84">
-        <v>262.8</v>
-      </c>
-      <c r="P84" t="s">
-        <v>163</v>
-      </c>
-      <c r="R84">
-        <v>4</v>
+      <c r="R84" t="s">
+        <v>553</v>
+      </c>
+      <c r="S84">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -6055,25 +6274,28 @@
         <v>347</v>
       </c>
       <c r="J85" s="1">
-        <v>0.001902494417246</v>
+        <v>0.001902465194929789</v>
       </c>
       <c r="K85" t="s">
         <v>347</v>
+      </c>
+      <c r="L85" s="1">
+        <v>0</v>
       </c>
       <c r="M85">
         <v>3</v>
       </c>
-      <c r="N85">
+      <c r="O85">
+        <v>4</v>
+      </c>
+      <c r="Q85">
         <v>325.875</v>
       </c>
-      <c r="O85">
-        <v>325.875</v>
-      </c>
-      <c r="P85" t="s">
-        <v>163</v>
-      </c>
-      <c r="R85">
-        <v>4</v>
+      <c r="R85" t="s">
+        <v>553</v>
+      </c>
+      <c r="S85">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -6105,25 +6327,28 @@
         <v>347</v>
       </c>
       <c r="J86" s="1">
-        <v>0.0018431801197156</v>
+        <v>0.001843180088510112</v>
       </c>
       <c r="K86" t="s">
         <v>347</v>
+      </c>
+      <c r="L86" s="1">
+        <v>0</v>
       </c>
       <c r="M86">
         <v>3</v>
       </c>
-      <c r="N86">
+      <c r="O86">
+        <v>4</v>
+      </c>
+      <c r="Q86">
         <v>315.72</v>
       </c>
-      <c r="O86">
-        <v>315.72</v>
-      </c>
-      <c r="P86" t="s">
-        <v>163</v>
-      </c>
-      <c r="R86">
-        <v>4</v>
+      <c r="R86" t="s">
+        <v>553</v>
+      </c>
+      <c r="S86">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -6155,25 +6380,28 @@
         <v>347</v>
       </c>
       <c r="J87" s="1">
-        <v>0.0043300020999363</v>
+        <v>0.004330002026628232</v>
       </c>
       <c r="K87" t="s">
         <v>347</v>
+      </c>
+      <c r="L87" s="1">
+        <v>0</v>
       </c>
       <c r="M87">
         <v>3</v>
       </c>
-      <c r="N87">
+      <c r="O87">
+        <v>4</v>
+      </c>
+      <c r="Q87">
         <v>741.6899999999999</v>
       </c>
-      <c r="O87">
-        <v>741.6899999999999</v>
-      </c>
-      <c r="P87" t="s">
-        <v>163</v>
-      </c>
-      <c r="R87">
-        <v>4</v>
+      <c r="R87" t="s">
+        <v>553</v>
+      </c>
+      <c r="S87">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -6196,28 +6424,31 @@
         <v>347</v>
       </c>
       <c r="I88" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="J88" s="1">
-        <v>0.9788348955586728</v>
+        <v>0.9788349017550247</v>
       </c>
       <c r="K88" t="s">
         <v>347</v>
+      </c>
+      <c r="L88" s="1">
+        <v>0</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>668853.9595999999</v>
-      </c>
-      <c r="P88" t="s">
-        <v>555</v>
+        <v>4.02</v>
       </c>
       <c r="Q88">
-        <v>4.02</v>
+        <v>167665.5239</v>
+      </c>
+      <c r="R88" t="s">
+        <v>553</v>
+      </c>
+      <c r="S88">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="89" spans="1:19">
@@ -6243,22 +6474,25 @@
         <v>347</v>
       </c>
       <c r="J89" s="1">
-        <v>0.0052779800165694</v>
+        <v>0.005277968251169266</v>
       </c>
       <c r="K89" t="s">
         <v>347</v>
+      </c>
+      <c r="L89" s="1">
+        <v>0</v>
       </c>
       <c r="M89">
         <v>2</v>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
+      <c r="Q89">
         <v>904.068</v>
       </c>
-      <c r="P89" t="s">
-        <v>555</v>
+      <c r="R89" t="s">
+        <v>553</v>
+      </c>
+      <c r="S89">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -6290,25 +6524,28 @@
         <v>347</v>
       </c>
       <c r="J90" s="1">
-        <v>0.0049715422727335</v>
+        <v>0.00497154218856405</v>
       </c>
       <c r="K90" t="s">
         <v>347</v>
+      </c>
+      <c r="L90" s="1">
+        <v>0</v>
       </c>
       <c r="M90">
         <v>3</v>
       </c>
-      <c r="N90">
+      <c r="O90">
+        <v>4</v>
+      </c>
+      <c r="Q90">
         <v>851.58</v>
       </c>
-      <c r="O90">
-        <v>851.58</v>
-      </c>
-      <c r="P90" t="s">
-        <v>169</v>
-      </c>
-      <c r="R90">
-        <v>4</v>
+      <c r="R90" t="s">
+        <v>553</v>
+      </c>
+      <c r="S90">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -6340,25 +6577,28 @@
         <v>347</v>
       </c>
       <c r="J91" s="1">
-        <v>0.0001102218442297</v>
+        <v>0.0001102335184063346</v>
       </c>
       <c r="K91" t="s">
         <v>347</v>
+      </c>
+      <c r="L91" s="1">
+        <v>0</v>
       </c>
       <c r="M91">
         <v>3</v>
       </c>
-      <c r="N91">
+      <c r="O91">
+        <v>4</v>
+      </c>
+      <c r="Q91">
         <v>18.882</v>
       </c>
-      <c r="O91">
-        <v>18.882</v>
-      </c>
-      <c r="P91" t="s">
-        <v>169</v>
-      </c>
-      <c r="R91">
-        <v>4</v>
+      <c r="R91" t="s">
+        <v>553</v>
+      </c>
+      <c r="S91">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -6390,25 +6630,28 @@
         <v>347</v>
       </c>
       <c r="J92" s="1">
-        <v>0.0001962158996061</v>
+        <v>0.0001961925441988814</v>
       </c>
       <c r="K92" t="s">
         <v>347</v>
+      </c>
+      <c r="L92" s="1">
+        <v>0</v>
       </c>
       <c r="M92">
         <v>3</v>
       </c>
-      <c r="N92">
+      <c r="O92">
+        <v>4</v>
+      </c>
+      <c r="Q92">
         <v>33.606</v>
       </c>
-      <c r="O92">
-        <v>33.606</v>
-      </c>
-      <c r="P92" t="s">
-        <v>169</v>
-      </c>
-      <c r="R92">
-        <v>4</v>
+      <c r="R92" t="s">
+        <v>553</v>
+      </c>
+      <c r="S92">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="93" spans="1:19">
@@ -6434,22 +6677,25 @@
         <v>347</v>
       </c>
       <c r="J93" s="1">
-        <v>0.9735569155421032</v>
+        <v>0.9735569335038555</v>
       </c>
       <c r="K93" t="s">
         <v>347</v>
+      </c>
+      <c r="L93" s="1">
+        <v>0</v>
       </c>
       <c r="M93">
         <v>2</v>
       </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>333522.9117999999</v>
-      </c>
-      <c r="P93" t="s">
-        <v>555</v>
+      <c r="Q93">
+        <v>166761.4559</v>
+      </c>
+      <c r="R93" t="s">
+        <v>553</v>
+      </c>
+      <c r="S93">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -6475,25 +6721,28 @@
         <v>347</v>
       </c>
       <c r="J94" s="1">
-        <v>0.4490209667284737</v>
+        <v>0.4490209293525225</v>
       </c>
       <c r="K94" t="s">
         <v>347</v>
+      </c>
+      <c r="L94" s="1">
+        <v>0</v>
       </c>
       <c r="M94">
         <v>3</v>
       </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
       <c r="O94">
+        <v>4</v>
+      </c>
+      <c r="Q94">
         <v>76913.20489999998</v>
       </c>
-      <c r="P94" t="s">
-        <v>169</v>
-      </c>
-      <c r="R94">
-        <v>4</v>
+      <c r="R94" t="s">
+        <v>553</v>
+      </c>
+      <c r="S94">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="95" spans="1:19">
@@ -6525,22 +6774,25 @@
         <v>347</v>
       </c>
       <c r="J95" s="1">
-        <v>0.1278140211876975</v>
+        <v>0.1278140306998154</v>
       </c>
       <c r="K95" t="s">
         <v>347</v>
+      </c>
+      <c r="L95" s="1">
+        <v>0</v>
       </c>
       <c r="M95">
         <v>4</v>
       </c>
-      <c r="N95">
+      <c r="Q95">
         <v>21893.382</v>
       </c>
-      <c r="O95">
-        <v>21893.382</v>
-      </c>
-      <c r="P95" t="s">
-        <v>174</v>
+      <c r="R95" t="s">
+        <v>553</v>
+      </c>
+      <c r="S95">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -6572,25 +6824,28 @@
         <v>347</v>
       </c>
       <c r="J96" s="1">
-        <v>0.3194964636477206</v>
+        <v>0.3194964582385619</v>
       </c>
       <c r="K96" t="s">
         <v>347</v>
+      </c>
+      <c r="L96" s="1">
+        <v>0</v>
       </c>
       <c r="M96">
         <v>4</v>
       </c>
-      <c r="N96">
+      <c r="Q96">
         <v>54726.84</v>
       </c>
-      <c r="O96">
-        <v>54726.84</v>
-      </c>
-      <c r="P96" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18">
+      <c r="R96" t="s">
+        <v>553</v>
+      </c>
+      <c r="S96">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" t="s">
         <v>22</v>
       </c>
@@ -6619,25 +6874,28 @@
         <v>347</v>
       </c>
       <c r="J97" s="1">
-        <v>0.0013776562924442</v>
+        <v>0.001377656269120158</v>
       </c>
       <c r="K97" t="s">
         <v>347</v>
+      </c>
+      <c r="L97" s="1">
+        <v>0</v>
       </c>
       <c r="M97">
         <v>4</v>
       </c>
-      <c r="N97">
+      <c r="Q97">
         <v>235.98</v>
       </c>
-      <c r="O97">
-        <v>235.98</v>
-      </c>
-      <c r="P97" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18">
+      <c r="R97" t="s">
+        <v>553</v>
+      </c>
+      <c r="S97">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
       <c r="A98" t="s">
         <v>22</v>
       </c>
@@ -6666,25 +6924,28 @@
         <v>347</v>
       </c>
       <c r="J98" s="1">
-        <v>0.0003307239129034</v>
+        <v>0.0003307005552190037</v>
       </c>
       <c r="K98" t="s">
         <v>347</v>
+      </c>
+      <c r="L98" s="1">
+        <v>0</v>
       </c>
       <c r="M98">
         <v>4</v>
       </c>
-      <c r="N98">
+      <c r="Q98">
         <v>56.64600000000001</v>
       </c>
-      <c r="O98">
-        <v>56.64600000000001</v>
-      </c>
-      <c r="P98" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18">
+      <c r="R98" t="s">
+        <v>553</v>
+      </c>
+      <c r="S98">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
       <c r="A99" t="s">
         <v>22</v>
       </c>
@@ -6713,25 +6974,28 @@
         <v>347</v>
       </c>
       <c r="J99" s="1">
-        <v>2.101687707771533E-06</v>
+        <v>2.083589806123335E-06</v>
       </c>
       <c r="K99" t="s">
         <v>347</v>
+      </c>
+      <c r="L99" s="1">
+        <v>0</v>
       </c>
       <c r="M99">
         <v>4</v>
       </c>
-      <c r="N99">
+      <c r="Q99">
         <v>0.3569</v>
       </c>
-      <c r="O99">
-        <v>0.3569</v>
-      </c>
-      <c r="P99" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18">
+      <c r="R99" t="s">
+        <v>553</v>
+      </c>
+      <c r="S99">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -6754,28 +7018,31 @@
         <v>347</v>
       </c>
       <c r="J100" s="1">
-        <v>0.5245359488136295</v>
+        <v>0.5245360041513329</v>
       </c>
       <c r="K100" t="s">
         <v>347</v>
+      </c>
+      <c r="L100" s="1">
+        <v>0</v>
       </c>
       <c r="M100">
         <v>3</v>
       </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
       <c r="O100">
+        <v>4</v>
+      </c>
+      <c r="Q100">
         <v>89848.251</v>
       </c>
-      <c r="P100" t="s">
-        <v>169</v>
-      </c>
-      <c r="R100">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18">
+      <c r="R100" t="s">
+        <v>553</v>
+      </c>
+      <c r="S100">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
       <c r="A101" t="s">
         <v>22</v>
       </c>
@@ -6804,25 +7071,28 @@
         <v>347</v>
       </c>
       <c r="J101" s="1">
-        <v>0.0067763665917823</v>
+        <v>0.006776366477056706</v>
       </c>
       <c r="K101" t="s">
         <v>347</v>
+      </c>
+      <c r="L101" s="1">
+        <v>0</v>
       </c>
       <c r="M101">
         <v>4</v>
       </c>
-      <c r="N101">
+      <c r="Q101">
         <v>1160.73</v>
       </c>
-      <c r="O101">
-        <v>1160.73</v>
-      </c>
-      <c r="P101" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18">
+      <c r="R101" t="s">
+        <v>553</v>
+      </c>
+      <c r="S101">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
       <c r="A102" t="s">
         <v>22</v>
       </c>
@@ -6851,25 +7121,28 @@
         <v>347</v>
       </c>
       <c r="J102" s="1">
-        <v>0.1276775282471206</v>
+        <v>0.1276775260855067</v>
       </c>
       <c r="K102" t="s">
         <v>347</v>
+      </c>
+      <c r="L102" s="1">
+        <v>0</v>
       </c>
       <c r="M102">
         <v>4</v>
       </c>
-      <c r="N102">
+      <c r="Q102">
         <v>21870</v>
       </c>
-      <c r="O102">
-        <v>21870</v>
-      </c>
-      <c r="P102" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18">
+      <c r="R102" t="s">
+        <v>553</v>
+      </c>
+      <c r="S102">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -6898,25 +7171,28 @@
         <v>347</v>
       </c>
       <c r="J103" s="1">
-        <v>0.1631435083157652</v>
+        <v>0.163143505553703</v>
       </c>
       <c r="K103" t="s">
         <v>347</v>
+      </c>
+      <c r="L103" s="1">
+        <v>0</v>
       </c>
       <c r="M103">
         <v>4</v>
       </c>
-      <c r="N103">
+      <c r="Q103">
         <v>27945</v>
       </c>
-      <c r="O103">
-        <v>27945</v>
-      </c>
-      <c r="P103" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18">
+      <c r="R103" t="s">
+        <v>553</v>
+      </c>
+      <c r="S103">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -6945,25 +7221,28 @@
         <v>347</v>
       </c>
       <c r="J104" s="1">
-        <v>0.1533335890386711</v>
+        <v>0.1533336156327999</v>
       </c>
       <c r="K104" t="s">
         <v>347</v>
+      </c>
+      <c r="L104" s="1">
+        <v>0</v>
       </c>
       <c r="M104">
         <v>4</v>
       </c>
-      <c r="N104">
+      <c r="Q104">
         <v>26264.655</v>
       </c>
-      <c r="O104">
-        <v>26264.655</v>
-      </c>
-      <c r="P104" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18">
+      <c r="R104" t="s">
+        <v>553</v>
+      </c>
+      <c r="S104">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -6992,25 +7271,28 @@
         <v>347</v>
       </c>
       <c r="J105" s="1">
-        <v>0.0034671425354678</v>
+        <v>0.003467154152810869</v>
       </c>
       <c r="K105" t="s">
         <v>347</v>
+      </c>
+      <c r="L105" s="1">
+        <v>0</v>
       </c>
       <c r="M105">
         <v>4</v>
       </c>
-      <c r="N105">
+      <c r="Q105">
         <v>593.8919999999999</v>
       </c>
-      <c r="O105">
-        <v>593.8919999999999</v>
-      </c>
-      <c r="P105" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18">
+      <c r="R105" t="s">
+        <v>553</v>
+      </c>
+      <c r="S105">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -7039,25 +7321,28 @@
         <v>347</v>
       </c>
       <c r="J106" s="1">
-        <v>0.0111364928821967</v>
+        <v>0.01113647517958905</v>
       </c>
       <c r="K106" t="s">
         <v>347</v>
+      </c>
+      <c r="L106" s="1">
+        <v>0</v>
       </c>
       <c r="M106">
         <v>4</v>
       </c>
-      <c r="N106">
+      <c r="Q106">
         <v>1907.577</v>
       </c>
-      <c r="O106">
-        <v>1907.577</v>
-      </c>
-      <c r="P106" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18">
+      <c r="R106" t="s">
+        <v>553</v>
+      </c>
+      <c r="S106">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -7086,25 +7371,28 @@
         <v>347</v>
       </c>
       <c r="J107" s="1">
-        <v>0.0300806972185505</v>
+        <v>0.03008066751916996</v>
       </c>
       <c r="K107" t="s">
         <v>347</v>
+      </c>
+      <c r="L107" s="1">
+        <v>0</v>
       </c>
       <c r="M107">
         <v>4</v>
       </c>
-      <c r="N107">
+      <c r="Q107">
         <v>5152.545</v>
       </c>
-      <c r="O107">
-        <v>5152.545</v>
-      </c>
-      <c r="P107" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18">
+      <c r="R107" t="s">
+        <v>553</v>
+      </c>
+      <c r="S107">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -7133,25 +7421,28 @@
         <v>347</v>
       </c>
       <c r="J108" s="1">
-        <v>0.0001707037460423</v>
+        <v>0.0001707095811735848</v>
       </c>
       <c r="K108" t="s">
         <v>347</v>
+      </c>
+      <c r="L108" s="1">
+        <v>0</v>
       </c>
       <c r="M108">
         <v>4</v>
       </c>
-      <c r="N108">
+      <c r="Q108">
         <v>29.241</v>
       </c>
-      <c r="O108">
-        <v>29.241</v>
-      </c>
-      <c r="P108" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18">
+      <c r="R108" t="s">
+        <v>553</v>
+      </c>
+      <c r="S108">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -7180,25 +7471,28 @@
         <v>347</v>
       </c>
       <c r="J109" s="1">
-        <v>0.008674949534683399</v>
+        <v>0.008674978577920813</v>
       </c>
       <c r="K109" t="s">
         <v>347</v>
+      </c>
+      <c r="L109" s="1">
+        <v>0</v>
       </c>
       <c r="M109">
         <v>4</v>
       </c>
-      <c r="N109">
+      <c r="Q109">
         <v>1485.945</v>
       </c>
-      <c r="O109">
-        <v>1485.945</v>
-      </c>
-      <c r="P109" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18">
+      <c r="R109" t="s">
+        <v>553</v>
+      </c>
+      <c r="S109">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -7227,25 +7521,28 @@
         <v>347</v>
       </c>
       <c r="J110" s="1">
-        <v>0.0049923256289548</v>
+        <v>0.004992348896518725</v>
       </c>
       <c r="K110" t="s">
         <v>347</v>
+      </c>
+      <c r="L110" s="1">
+        <v>0</v>
       </c>
       <c r="M110">
         <v>4</v>
       </c>
-      <c r="N110">
+      <c r="Q110">
         <v>855.144</v>
       </c>
-      <c r="O110">
-        <v>855.144</v>
-      </c>
-      <c r="P110" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18">
+      <c r="R110" t="s">
+        <v>553</v>
+      </c>
+      <c r="S110">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -7274,25 +7571,28 @@
         <v>347</v>
       </c>
       <c r="J111" s="1">
-        <v>0.0069018256718935</v>
+        <v>0.006901837231086415</v>
       </c>
       <c r="K111" t="s">
         <v>347</v>
+      </c>
+      <c r="L111" s="1">
+        <v>0</v>
       </c>
       <c r="M111">
         <v>4</v>
       </c>
-      <c r="N111">
+      <c r="Q111">
         <v>1182.222</v>
       </c>
-      <c r="O111">
-        <v>1182.222</v>
-      </c>
-      <c r="P111" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18">
+      <c r="R111" t="s">
+        <v>553</v>
+      </c>
+      <c r="S111">
+        <v>342581.8258</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -7321,22 +7621,25 @@
         <v>347</v>
       </c>
       <c r="J112" s="1">
-        <v>0.008180819402500599</v>
+        <v>0.00818081926399728</v>
       </c>
       <c r="K112" t="s">
         <v>347</v>
+      </c>
+      <c r="L112" s="1">
+        <v>0</v>
       </c>
       <c r="M112">
         <v>4</v>
       </c>
-      <c r="N112">
+      <c r="Q112">
         <v>1401.3</v>
       </c>
-      <c r="O112">
-        <v>1401.3</v>
-      </c>
-      <c r="P112" t="s">
-        <v>174</v>
+      <c r="R112" t="s">
+        <v>553</v>
+      </c>
+      <c r="S112">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -7359,28 +7662,31 @@
         <v>347</v>
       </c>
       <c r="I113" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J113" s="1">
-        <v>0.011555195777756</v>
+        <v>0.01155521893420886</v>
       </c>
       <c r="K113" t="s">
         <v>347</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0</v>
       </c>
       <c r="M113">
         <v>1</v>
       </c>
       <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>3958.608</v>
-      </c>
-      <c r="P113" t="s">
-        <v>555</v>
+        <v>4.03</v>
       </c>
       <c r="Q113">
-        <v>4.03</v>
+        <v>1979.304</v>
+      </c>
+      <c r="R113" t="s">
+        <v>553</v>
+      </c>
+      <c r="S113">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -7406,22 +7712,25 @@
         <v>347</v>
       </c>
       <c r="J114" s="1">
-        <v>0.0035670310818011</v>
+        <v>0.00356703102141036</v>
       </c>
       <c r="K114" t="s">
         <v>347</v>
+      </c>
+      <c r="L114" s="1">
+        <v>0</v>
       </c>
       <c r="M114">
         <v>2</v>
       </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
+      <c r="Q114">
         <v>611</v>
       </c>
-      <c r="P114" t="s">
-        <v>555</v>
+      <c r="R114" t="s">
+        <v>553</v>
+      </c>
+      <c r="S114">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -7453,25 +7762,28 @@
         <v>347</v>
       </c>
       <c r="J115" s="1">
-        <v>0.0035670310818011</v>
+        <v>0.00356703102141036</v>
       </c>
       <c r="K115" t="s">
         <v>347</v>
+      </c>
+      <c r="L115" s="1">
+        <v>0</v>
       </c>
       <c r="M115">
         <v>3</v>
       </c>
-      <c r="N115">
+      <c r="O115">
+        <v>4</v>
+      </c>
+      <c r="Q115">
         <v>611</v>
       </c>
-      <c r="O115">
-        <v>611</v>
-      </c>
-      <c r="P115" t="s">
-        <v>194</v>
-      </c>
-      <c r="R115">
-        <v>4</v>
+      <c r="R115" t="s">
+        <v>553</v>
+      </c>
+      <c r="S115">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -7497,22 +7809,25 @@
         <v>347</v>
       </c>
       <c r="J116" s="1">
-        <v>0.0079881646959549</v>
+        <v>0.007988187912798497</v>
       </c>
       <c r="K116" t="s">
         <v>347</v>
+      </c>
+      <c r="L116" s="1">
+        <v>0</v>
       </c>
       <c r="M116">
         <v>2</v>
       </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
+      <c r="Q116">
         <v>1368.304</v>
       </c>
-      <c r="P116" t="s">
-        <v>555</v>
+      <c r="R116" t="s">
+        <v>553</v>
+      </c>
+      <c r="S116">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -7544,25 +7859,28 @@
         <v>347</v>
       </c>
       <c r="J117" s="1">
-        <v>0.0079881646959549</v>
+        <v>0.007988187912798497</v>
       </c>
       <c r="K117" t="s">
         <v>347</v>
+      </c>
+      <c r="L117" s="1">
+        <v>0</v>
       </c>
       <c r="M117">
         <v>3</v>
       </c>
-      <c r="N117">
+      <c r="O117">
+        <v>4</v>
+      </c>
+      <c r="Q117">
         <v>1368.304</v>
       </c>
-      <c r="O117">
-        <v>1368.304</v>
-      </c>
-      <c r="P117" t="s">
-        <v>194</v>
-      </c>
-      <c r="R117">
-        <v>4</v>
+      <c r="R117" t="s">
+        <v>553</v>
+      </c>
+      <c r="S117">
+        <v>342581.8258</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -7588,28 +7906,25 @@
         <v>347</v>
       </c>
       <c r="K118" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L118" s="1">
-        <v>0.1294789904825823</v>
+        <v>0.0960538877637785</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>986981.9739999999</v>
-      </c>
-      <c r="P118" t="s">
+        <v>5</v>
+      </c>
+      <c r="P118">
+        <v>246745.4935</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118" t="s">
         <v>199</v>
-      </c>
-      <c r="Q118">
-        <v>5</v>
-      </c>
-      <c r="S118">
-        <v>246745.4935</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -7632,28 +7947,31 @@
         <v>347</v>
       </c>
       <c r="I119" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J119" s="1">
-        <v>0.9694461961446744</v>
+        <v>0.9694463153386832</v>
       </c>
       <c r="K119" t="s">
         <v>347</v>
+      </c>
+      <c r="L119" s="1">
+        <v>0</v>
       </c>
       <c r="M119">
         <v>1</v>
       </c>
       <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>478413.019</v>
-      </c>
-      <c r="P119" t="s">
-        <v>556</v>
+        <v>5.01</v>
       </c>
       <c r="Q119">
-        <v>5.01</v>
+        <v>239206.5095</v>
+      </c>
+      <c r="R119" t="s">
+        <v>554</v>
+      </c>
+      <c r="S119">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -7679,22 +7997,25 @@
         <v>347</v>
       </c>
       <c r="J120" s="1">
-        <v>0.1493240373439072</v>
+        <v>0.1493277748555922</v>
       </c>
       <c r="K120" t="s">
         <v>347</v>
+      </c>
+      <c r="L120" s="1">
+        <v>0</v>
       </c>
       <c r="M120">
         <v>2</v>
       </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
+      <c r="Q120">
         <v>36845.9555</v>
       </c>
-      <c r="P120" t="s">
-        <v>556</v>
+      <c r="R120" t="s">
+        <v>554</v>
+      </c>
+      <c r="S120">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -7726,25 +8047,28 @@
         <v>347</v>
       </c>
       <c r="J121" s="1">
-        <v>0.0238398115620861</v>
+        <v>0.02383970591138679</v>
       </c>
       <c r="K121" t="s">
         <v>347</v>
+      </c>
+      <c r="L121" s="1">
+        <v>0</v>
       </c>
       <c r="M121">
         <v>3</v>
       </c>
-      <c r="N121">
+      <c r="O121">
+        <v>5</v>
+      </c>
+      <c r="Q121">
         <v>5882.34</v>
       </c>
-      <c r="O121">
-        <v>5882.34</v>
-      </c>
-      <c r="P121" t="s">
-        <v>200</v>
-      </c>
-      <c r="R121">
-        <v>5</v>
+      <c r="R121" t="s">
+        <v>554</v>
+      </c>
+      <c r="S121">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -7776,25 +8100,28 @@
         <v>347</v>
       </c>
       <c r="J122" s="1">
-        <v>0.0295616435469254</v>
+        <v>0.0295659097822591</v>
       </c>
       <c r="K122" t="s">
         <v>347</v>
+      </c>
+      <c r="L122" s="1">
+        <v>0</v>
       </c>
       <c r="M122">
         <v>3</v>
       </c>
-      <c r="N122">
+      <c r="O122">
+        <v>5</v>
+      </c>
+      <c r="Q122">
         <v>7295.254999999999</v>
       </c>
-      <c r="O122">
-        <v>7295.254999999999</v>
-      </c>
-      <c r="P122" t="s">
-        <v>200</v>
-      </c>
-      <c r="R122">
-        <v>5</v>
+      <c r="R122" t="s">
+        <v>554</v>
+      </c>
+      <c r="S122">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -7826,25 +8153,28 @@
         <v>347</v>
       </c>
       <c r="J123" s="1">
-        <v>0.0286404473617233</v>
+        <v>0.0286403042250496</v>
       </c>
       <c r="K123" t="s">
         <v>347</v>
+      </c>
+      <c r="L123" s="1">
+        <v>0</v>
       </c>
       <c r="M123">
         <v>3</v>
       </c>
-      <c r="N123">
+      <c r="O123">
+        <v>5</v>
+      </c>
+      <c r="Q123">
         <v>7066.865999999999</v>
       </c>
-      <c r="O123">
-        <v>7066.865999999999</v>
-      </c>
-      <c r="P123" t="s">
-        <v>200</v>
-      </c>
-      <c r="R123">
-        <v>5</v>
+      <c r="R123" t="s">
+        <v>554</v>
+      </c>
+      <c r="S123">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -7876,25 +8206,28 @@
         <v>347</v>
       </c>
       <c r="J124" s="1">
-        <v>0.0672821348731724</v>
+        <v>0.06728185493689674</v>
       </c>
       <c r="K124" t="s">
         <v>347</v>
+      </c>
+      <c r="L124" s="1">
+        <v>0</v>
       </c>
       <c r="M124">
         <v>3</v>
       </c>
-      <c r="N124">
+      <c r="O124">
+        <v>5</v>
+      </c>
+      <c r="Q124">
         <v>16601.4945</v>
       </c>
-      <c r="O124">
-        <v>16601.4945</v>
-      </c>
-      <c r="P124" t="s">
-        <v>200</v>
-      </c>
-      <c r="R124">
-        <v>5</v>
+      <c r="R124" t="s">
+        <v>554</v>
+      </c>
+      <c r="S124">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -7920,22 +8253,25 @@
         <v>347</v>
       </c>
       <c r="J125" s="1">
-        <v>0.8201221588007671</v>
+        <v>0.820118540483091</v>
       </c>
       <c r="K125" t="s">
         <v>347</v>
+      </c>
+      <c r="L125" s="1">
+        <v>0</v>
       </c>
       <c r="M125">
         <v>2</v>
       </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
+      <c r="Q125">
         <v>202360.554</v>
       </c>
-      <c r="P125" t="s">
-        <v>556</v>
+      <c r="R125" t="s">
+        <v>554</v>
+      </c>
+      <c r="S125">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -7967,25 +8303,28 @@
         <v>347</v>
       </c>
       <c r="J126" s="1">
-        <v>0.7725078664399272</v>
+        <v>0.7725044429230883</v>
       </c>
       <c r="K126" t="s">
         <v>347</v>
+      </c>
+      <c r="L126" s="1">
+        <v>0</v>
       </c>
       <c r="M126">
         <v>3</v>
       </c>
-      <c r="N126">
+      <c r="O126">
+        <v>5</v>
+      </c>
+      <c r="Q126">
         <v>190611.99</v>
       </c>
-      <c r="O126">
-        <v>190611.99</v>
-      </c>
-      <c r="P126" t="s">
-        <v>200</v>
-      </c>
-      <c r="R126">
-        <v>5</v>
+      <c r="R126" t="s">
+        <v>554</v>
+      </c>
+      <c r="S126">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -8017,25 +8356,28 @@
         <v>347</v>
       </c>
       <c r="J127" s="1">
-        <v>0.0171287372682014</v>
+        <v>0.01712866541167448</v>
       </c>
       <c r="K127" t="s">
         <v>347</v>
+      </c>
+      <c r="L127" s="1">
+        <v>0</v>
       </c>
       <c r="M127">
         <v>3</v>
       </c>
-      <c r="N127">
+      <c r="O127">
+        <v>5</v>
+      </c>
+      <c r="Q127">
         <v>4226.421</v>
       </c>
-      <c r="O127">
-        <v>4226.421</v>
-      </c>
-      <c r="P127" t="s">
-        <v>200</v>
-      </c>
-      <c r="R127">
-        <v>5</v>
+      <c r="R127" t="s">
+        <v>554</v>
+      </c>
+      <c r="S127">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -8067,25 +8409,28 @@
         <v>347</v>
       </c>
       <c r="J128" s="1">
-        <v>0.0304855550926383</v>
+        <v>0.03048543214832818</v>
       </c>
       <c r="K128" t="s">
         <v>347</v>
+      </c>
+      <c r="L128" s="1">
+        <v>0</v>
       </c>
       <c r="M128">
         <v>3</v>
       </c>
-      <c r="N128">
+      <c r="O128">
+        <v>5</v>
+      </c>
+      <c r="Q128">
         <v>7522.143</v>
       </c>
-      <c r="O128">
-        <v>7522.143</v>
-      </c>
-      <c r="P128" t="s">
-        <v>200</v>
-      </c>
-      <c r="R128">
-        <v>5</v>
+      <c r="R128" t="s">
+        <v>554</v>
+      </c>
+      <c r="S128">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -8108,28 +8453,31 @@
         <v>347</v>
       </c>
       <c r="I129" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J129" s="1">
-        <v>0.0305538038553255</v>
+        <v>0.03055368466131683</v>
       </c>
       <c r="K129" t="s">
         <v>347</v>
+      </c>
+      <c r="L129" s="1">
+        <v>0</v>
       </c>
       <c r="M129">
         <v>1</v>
       </c>
       <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>15077.968</v>
-      </c>
-      <c r="P129" t="s">
-        <v>556</v>
+        <v>5.02</v>
       </c>
       <c r="Q129">
-        <v>5.02</v>
+        <v>7538.984</v>
+      </c>
+      <c r="R129" t="s">
+        <v>554</v>
+      </c>
+      <c r="S129">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -8155,22 +8503,25 @@
         <v>347</v>
       </c>
       <c r="J130" s="1">
-        <v>0.0180766007252849</v>
+        <v>0.0180765206153603</v>
       </c>
       <c r="K130" t="s">
         <v>347</v>
+      </c>
+      <c r="L130" s="1">
+        <v>0</v>
       </c>
       <c r="M130">
         <v>2</v>
       </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
+      <c r="Q130">
         <v>4460.3</v>
       </c>
-      <c r="P130" t="s">
-        <v>556</v>
+      <c r="R130" t="s">
+        <v>554</v>
+      </c>
+      <c r="S130">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -8202,25 +8553,28 @@
         <v>347</v>
       </c>
       <c r="J131" s="1">
-        <v>0.0180766007252849</v>
+        <v>0.0180765206153603</v>
       </c>
       <c r="K131" t="s">
         <v>347</v>
+      </c>
+      <c r="L131" s="1">
+        <v>0</v>
       </c>
       <c r="M131">
         <v>3</v>
       </c>
-      <c r="N131">
+      <c r="O131">
+        <v>5</v>
+      </c>
+      <c r="Q131">
         <v>4460.3</v>
       </c>
-      <c r="O131">
-        <v>4460.3</v>
-      </c>
-      <c r="P131" t="s">
-        <v>210</v>
-      </c>
-      <c r="R131">
-        <v>5</v>
+      <c r="R131" t="s">
+        <v>554</v>
+      </c>
+      <c r="S131">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -8246,22 +8600,25 @@
         <v>347</v>
       </c>
       <c r="J132" s="1">
-        <v>0.0124772031300406</v>
+        <v>0.01247716404595653</v>
       </c>
       <c r="K132" t="s">
         <v>347</v>
+      </c>
+      <c r="L132" s="1">
+        <v>0</v>
       </c>
       <c r="M132">
         <v>2</v>
       </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
+      <c r="Q132">
         <v>3078.684</v>
       </c>
-      <c r="P132" t="s">
-        <v>556</v>
+      <c r="R132" t="s">
+        <v>554</v>
+      </c>
+      <c r="S132">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -8293,25 +8650,28 @@
         <v>347</v>
       </c>
       <c r="J133" s="1">
-        <v>0.0124772031300406</v>
+        <v>0.01247716404595653</v>
       </c>
       <c r="K133" t="s">
         <v>347</v>
+      </c>
+      <c r="L133" s="1">
+        <v>0</v>
       </c>
       <c r="M133">
         <v>3</v>
       </c>
-      <c r="N133">
+      <c r="O133">
+        <v>5</v>
+      </c>
+      <c r="Q133">
         <v>3078.684</v>
       </c>
-      <c r="O133">
-        <v>3078.684</v>
-      </c>
-      <c r="P133" t="s">
-        <v>210</v>
-      </c>
-      <c r="R133">
-        <v>5</v>
+      <c r="R133" t="s">
+        <v>554</v>
+      </c>
+      <c r="S133">
+        <v>493490.987</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -8337,28 +8697,25 @@
         <v>347</v>
       </c>
       <c r="K134" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L134" s="1">
-        <v>1</v>
+        <v>0.1932353558733015</v>
       </c>
       <c r="M134">
         <v>0</v>
       </c>
       <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>1985550.168</v>
-      </c>
-      <c r="P134" t="s">
+        <v>6</v>
+      </c>
+      <c r="P134">
+        <v>496387.542</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134" t="s">
         <v>215</v>
-      </c>
-      <c r="Q134">
-        <v>6</v>
-      </c>
-      <c r="S134">
-        <v>496387.542</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -8381,28 +8738,31 @@
         <v>347</v>
       </c>
       <c r="I135" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J135" s="1">
-        <v>0.0989108819736683</v>
+        <v>0.09891004073587326</v>
       </c>
       <c r="K135" t="s">
         <v>347</v>
+      </c>
+      <c r="L135" s="1">
+        <v>0</v>
       </c>
       <c r="M135">
         <v>1</v>
       </c>
       <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>98195.424</v>
-      </c>
-      <c r="P135" t="s">
-        <v>557</v>
+        <v>6.01</v>
       </c>
       <c r="Q135">
-        <v>6.01</v>
+        <v>49097.712</v>
+      </c>
+      <c r="R135" t="s">
+        <v>555</v>
+      </c>
+      <c r="S135">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -8428,22 +8788,25 @@
         <v>347</v>
       </c>
       <c r="J136" s="1">
-        <v>0.0303417741894217</v>
+        <v>0.03034151489643952</v>
       </c>
       <c r="K136" t="s">
         <v>347</v>
+      </c>
+      <c r="L136" s="1">
+        <v>0</v>
       </c>
       <c r="M136">
         <v>2</v>
       </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
+      <c r="Q136">
         <v>15061.15</v>
       </c>
-      <c r="P136" t="s">
-        <v>557</v>
+      <c r="R136" t="s">
+        <v>555</v>
+      </c>
+      <c r="S136">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -8475,25 +8838,28 @@
         <v>347</v>
       </c>
       <c r="J137" s="1">
-        <v>0.0303417741894217</v>
+        <v>0.03034151489643952</v>
       </c>
       <c r="K137" t="s">
         <v>347</v>
+      </c>
+      <c r="L137" s="1">
+        <v>0</v>
       </c>
       <c r="M137">
         <v>3</v>
       </c>
-      <c r="N137">
+      <c r="O137">
+        <v>6</v>
+      </c>
+      <c r="Q137">
         <v>15061.15</v>
       </c>
-      <c r="O137">
-        <v>15061.15</v>
-      </c>
-      <c r="P137" t="s">
-        <v>216</v>
-      </c>
-      <c r="R137">
-        <v>6</v>
+      <c r="R137" t="s">
+        <v>555</v>
+      </c>
+      <c r="S137">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -8519,22 +8885,25 @@
         <v>347</v>
       </c>
       <c r="J138" s="1">
-        <v>0.06856910778424651</v>
+        <v>0.06856852583943374</v>
       </c>
       <c r="K138" t="s">
         <v>347</v>
+      </c>
+      <c r="L138" s="1">
+        <v>0</v>
       </c>
       <c r="M138">
         <v>2</v>
       </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
+      <c r="Q138">
         <v>34036.562</v>
       </c>
-      <c r="P138" t="s">
-        <v>557</v>
+      <c r="R138" t="s">
+        <v>555</v>
+      </c>
+      <c r="S138">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -8566,25 +8935,28 @@
         <v>347</v>
       </c>
       <c r="J139" s="1">
-        <v>0.06856910778424651</v>
+        <v>0.06856852583943374</v>
       </c>
       <c r="K139" t="s">
         <v>347</v>
+      </c>
+      <c r="L139" s="1">
+        <v>0</v>
       </c>
       <c r="M139">
         <v>3</v>
       </c>
-      <c r="N139">
+      <c r="O139">
+        <v>6</v>
+      </c>
+      <c r="Q139">
         <v>34036.562</v>
       </c>
-      <c r="O139">
-        <v>34036.562</v>
-      </c>
-      <c r="P139" t="s">
-        <v>216</v>
-      </c>
-      <c r="R139">
-        <v>6</v>
+      <c r="R139" t="s">
+        <v>555</v>
+      </c>
+      <c r="S139">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -8607,28 +8979,31 @@
         <v>347</v>
       </c>
       <c r="I140" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J140" s="1">
-        <v>0.864618995038713</v>
+        <v>0.8646201479407798</v>
       </c>
       <c r="K140" t="s">
         <v>347</v>
+      </c>
+      <c r="L140" s="1">
+        <v>0</v>
       </c>
       <c r="M140">
         <v>1</v>
       </c>
       <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>858373.34</v>
-      </c>
-      <c r="P140" t="s">
-        <v>557</v>
+        <v>6.02</v>
       </c>
       <c r="Q140">
-        <v>6.02</v>
+        <v>429186.67</v>
+      </c>
+      <c r="R140" t="s">
+        <v>555</v>
+      </c>
+      <c r="S140">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -8654,22 +9029,25 @@
         <v>347</v>
       </c>
       <c r="J141" s="1">
-        <v>0.0611808858194866</v>
+        <v>0.06118035895429463</v>
       </c>
       <c r="K141" t="s">
         <v>347</v>
+      </c>
+      <c r="L141" s="1">
+        <v>0</v>
       </c>
       <c r="M141">
         <v>2</v>
       </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
+      <c r="Q141">
         <v>30369.168</v>
       </c>
-      <c r="P141" t="s">
-        <v>557</v>
+      <c r="R141" t="s">
+        <v>555</v>
+      </c>
+      <c r="S141">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -8701,25 +9079,28 @@
         <v>347</v>
       </c>
       <c r="J142" s="1">
-        <v>0.0611808858194866</v>
+        <v>0.06118035895429463</v>
       </c>
       <c r="K142" t="s">
         <v>347</v>
+      </c>
+      <c r="L142" s="1">
+        <v>0</v>
       </c>
       <c r="M142">
         <v>3</v>
       </c>
-      <c r="N142">
+      <c r="O142">
+        <v>6</v>
+      </c>
+      <c r="Q142">
         <v>30369.168</v>
       </c>
-      <c r="O142">
-        <v>30369.168</v>
-      </c>
-      <c r="P142" t="s">
-        <v>221</v>
-      </c>
-      <c r="R142">
-        <v>6</v>
+      <c r="R142" t="s">
+        <v>555</v>
+      </c>
+      <c r="S142">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -8745,22 +9126,25 @@
         <v>347</v>
       </c>
       <c r="J143" s="1">
-        <v>0.5807818071236482</v>
+        <v>0.5807853997270543</v>
       </c>
       <c r="K143" t="s">
         <v>347</v>
+      </c>
+      <c r="L143" s="1">
+        <v>0</v>
       </c>
       <c r="M143">
         <v>2</v>
       </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
+      <c r="Q143">
         <v>288294.637</v>
       </c>
-      <c r="P143" t="s">
-        <v>557</v>
+      <c r="R143" t="s">
+        <v>555</v>
+      </c>
+      <c r="S143">
+        <v>992775.084</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -8792,28 +9176,31 @@
         <v>347</v>
       </c>
       <c r="J144" s="1">
-        <v>0.0042536281941797</v>
+        <v>0.004253597887434492</v>
       </c>
       <c r="K144" t="s">
         <v>347</v>
+      </c>
+      <c r="L144" s="1">
+        <v>0</v>
       </c>
       <c r="M144">
         <v>3</v>
       </c>
-      <c r="N144">
+      <c r="O144">
+        <v>6</v>
+      </c>
+      <c r="Q144">
         <v>2111.433</v>
       </c>
-      <c r="O144">
-        <v>2111.433</v>
-      </c>
-      <c r="P144" t="s">
-        <v>221</v>
-      </c>
-      <c r="R144">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18">
+      <c r="R144" t="s">
+        <v>555</v>
+      </c>
+      <c r="S144">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19">
       <c r="A145" t="s">
         <v>24</v>
       </c>
@@ -8842,28 +9229,31 @@
         <v>347</v>
       </c>
       <c r="J145" s="1">
-        <v>0.0009389115226075999</v>
+        <v>0.0009389045061892387</v>
       </c>
       <c r="K145" t="s">
         <v>347</v>
+      </c>
+      <c r="L145" s="1">
+        <v>0</v>
       </c>
       <c r="M145">
         <v>3</v>
       </c>
-      <c r="N145">
+      <c r="O145">
+        <v>6</v>
+      </c>
+      <c r="Q145">
         <v>466.0605</v>
       </c>
-      <c r="O145">
-        <v>466.0605</v>
-      </c>
-      <c r="P145" t="s">
-        <v>221</v>
-      </c>
-      <c r="R145">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18">
+      <c r="R145" t="s">
+        <v>555</v>
+      </c>
+      <c r="S145">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19">
       <c r="A146" t="s">
         <v>24</v>
       </c>
@@ -8892,28 +9282,31 @@
         <v>347</v>
       </c>
       <c r="J146" s="1">
-        <v>0.0319416467072925</v>
+        <v>0.03194137374221209</v>
       </c>
       <c r="K146" t="s">
         <v>347</v>
+      </c>
+      <c r="L146" s="1">
+        <v>0</v>
       </c>
       <c r="M146">
         <v>3</v>
       </c>
-      <c r="N146">
+      <c r="O146">
+        <v>6</v>
+      </c>
+      <c r="Q146">
         <v>15855.3</v>
       </c>
-      <c r="O146">
-        <v>15855.3</v>
-      </c>
-      <c r="P146" t="s">
-        <v>221</v>
-      </c>
-      <c r="R146">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18">
+      <c r="R146" t="s">
+        <v>555</v>
+      </c>
+      <c r="S146">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
       <c r="A147" t="s">
         <v>24</v>
       </c>
@@ -8942,28 +9335,31 @@
         <v>347</v>
       </c>
       <c r="J147" s="1">
-        <v>0.0418120432335253</v>
+        <v>0.04181168793313511</v>
       </c>
       <c r="K147" t="s">
         <v>347</v>
+      </c>
+      <c r="L147" s="1">
+        <v>0</v>
       </c>
       <c r="M147">
         <v>3</v>
       </c>
-      <c r="N147">
+      <c r="O147">
+        <v>6</v>
+      </c>
+      <c r="Q147">
         <v>20754.801</v>
       </c>
-      <c r="O147">
-        <v>20754.801</v>
-      </c>
-      <c r="P147" t="s">
-        <v>221</v>
-      </c>
-      <c r="R147">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18">
+      <c r="R147" t="s">
+        <v>555</v>
+      </c>
+      <c r="S147">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
       <c r="A148" t="s">
         <v>24</v>
       </c>
@@ -8992,28 +9388,31 @@
         <v>347</v>
       </c>
       <c r="J148" s="1">
-        <v>0.0248943507970554</v>
+        <v>0.02489566931959787</v>
       </c>
       <c r="K148" t="s">
         <v>347</v>
+      </c>
+      <c r="L148" s="1">
+        <v>0</v>
       </c>
       <c r="M148">
         <v>3</v>
       </c>
-      <c r="N148">
+      <c r="O148">
+        <v>6</v>
+      </c>
+      <c r="Q148">
         <v>12357.9001</v>
       </c>
-      <c r="O148">
-        <v>12357.9001</v>
-      </c>
-      <c r="P148" t="s">
-        <v>221</v>
-      </c>
-      <c r="R148">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18">
+      <c r="R148" t="s">
+        <v>555</v>
+      </c>
+      <c r="S148">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
       <c r="A149" t="s">
         <v>24</v>
       </c>
@@ -9042,28 +9441,31 @@
         <v>347</v>
       </c>
       <c r="J149" s="1">
-        <v>0.0058956052711684</v>
+        <v>0.005895546830625334</v>
       </c>
       <c r="K149" t="s">
         <v>347</v>
+      </c>
+      <c r="L149" s="1">
+        <v>0</v>
       </c>
       <c r="M149">
         <v>3</v>
       </c>
-      <c r="N149">
+      <c r="O149">
+        <v>6</v>
+      </c>
+      <c r="Q149">
         <v>2926.476</v>
       </c>
-      <c r="O149">
-        <v>2926.476</v>
-      </c>
-      <c r="P149" t="s">
-        <v>221</v>
-      </c>
-      <c r="R149">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18">
+      <c r="R149" t="s">
+        <v>555</v>
+      </c>
+      <c r="S149">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
       <c r="A150" t="s">
         <v>24</v>
       </c>
@@ -9092,28 +9494,31 @@
         <v>347</v>
       </c>
       <c r="J150" s="1">
-        <v>0.0221292497148876</v>
+        <v>0.02212963555801729</v>
       </c>
       <c r="K150" t="s">
         <v>347</v>
+      </c>
+      <c r="L150" s="1">
+        <v>0</v>
       </c>
       <c r="M150">
         <v>3</v>
       </c>
-      <c r="N150">
+      <c r="O150">
+        <v>6</v>
+      </c>
+      <c r="Q150">
         <v>10984.8754</v>
       </c>
-      <c r="O150">
-        <v>10984.8754</v>
-      </c>
-      <c r="P150" t="s">
-        <v>221</v>
-      </c>
-      <c r="R150">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18">
+      <c r="R150" t="s">
+        <v>555</v>
+      </c>
+      <c r="S150">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19">
       <c r="A151" t="s">
         <v>24</v>
       </c>
@@ -9142,28 +9547,31 @@
         <v>347</v>
       </c>
       <c r="J151" s="1">
-        <v>0.08953248427173111</v>
+        <v>0.08953171834437375</v>
       </c>
       <c r="K151" t="s">
         <v>347</v>
+      </c>
+      <c r="L151" s="1">
+        <v>0</v>
       </c>
       <c r="M151">
         <v>3</v>
       </c>
-      <c r="N151">
+      <c r="O151">
+        <v>6</v>
+      </c>
+      <c r="Q151">
         <v>44442.4296</v>
       </c>
-      <c r="O151">
-        <v>44442.4296</v>
-      </c>
-      <c r="P151" t="s">
-        <v>221</v>
-      </c>
-      <c r="R151">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18">
+      <c r="R151" t="s">
+        <v>555</v>
+      </c>
+      <c r="S151">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19">
       <c r="A152" t="s">
         <v>24</v>
       </c>
@@ -9192,28 +9600,31 @@
         <v>347</v>
       </c>
       <c r="J152" s="1">
-        <v>0.0751401185333995</v>
+        <v>0.07513947962860035</v>
       </c>
       <c r="K152" t="s">
         <v>347</v>
+      </c>
+      <c r="L152" s="1">
+        <v>0</v>
       </c>
       <c r="M152">
         <v>3</v>
       </c>
-      <c r="N152">
+      <c r="O152">
+        <v>6</v>
+      </c>
+      <c r="Q152">
         <v>37298.3016</v>
       </c>
-      <c r="O152">
-        <v>37298.3016</v>
-      </c>
-      <c r="P152" t="s">
-        <v>221</v>
-      </c>
-      <c r="R152">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18">
+      <c r="R152" t="s">
+        <v>555</v>
+      </c>
+      <c r="S152">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -9242,28 +9653,31 @@
         <v>347</v>
       </c>
       <c r="J153" s="1">
-        <v>0.0376300330812902</v>
+        <v>0.03762970747561589</v>
       </c>
       <c r="K153" t="s">
         <v>347</v>
+      </c>
+      <c r="L153" s="1">
+        <v>0</v>
       </c>
       <c r="M153">
         <v>3</v>
       </c>
-      <c r="N153">
+      <c r="O153">
+        <v>6</v>
+      </c>
+      <c r="Q153">
         <v>18678.918</v>
       </c>
-      <c r="O153">
-        <v>18678.918</v>
-      </c>
-      <c r="P153" t="s">
-        <v>221</v>
-      </c>
-      <c r="R153">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18">
+      <c r="R153" t="s">
+        <v>555</v>
+      </c>
+      <c r="S153">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19">
       <c r="A154" t="s">
         <v>24</v>
       </c>
@@ -9292,28 +9706,31 @@
         <v>347</v>
       </c>
       <c r="J154" s="1">
-        <v>0.0076908308559131</v>
+        <v>0.007690757073834862</v>
       </c>
       <c r="K154" t="s">
         <v>347</v>
+      </c>
+      <c r="L154" s="1">
+        <v>0</v>
       </c>
       <c r="M154">
         <v>3</v>
       </c>
-      <c r="N154">
+      <c r="O154">
+        <v>6</v>
+      </c>
+      <c r="Q154">
         <v>3817.596</v>
       </c>
-      <c r="O154">
-        <v>3817.596</v>
-      </c>
-      <c r="P154" t="s">
-        <v>221</v>
-      </c>
-      <c r="R154">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18">
+      <c r="R154" t="s">
+        <v>555</v>
+      </c>
+      <c r="S154">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19">
       <c r="A155" t="s">
         <v>24</v>
       </c>
@@ -9342,28 +9759,31 @@
         <v>347</v>
       </c>
       <c r="J155" s="1">
-        <v>0.1425297950192925</v>
+        <v>0.1425350352567873</v>
       </c>
       <c r="K155" t="s">
         <v>347</v>
+      </c>
+      <c r="L155" s="1">
+        <v>0</v>
       </c>
       <c r="M155">
         <v>3</v>
       </c>
-      <c r="N155">
+      <c r="O155">
+        <v>6</v>
+      </c>
+      <c r="Q155">
         <v>70752.6158</v>
       </c>
-      <c r="O155">
-        <v>70752.6158</v>
-      </c>
-      <c r="P155" t="s">
-        <v>221</v>
-      </c>
-      <c r="R155">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18">
+      <c r="R155" t="s">
+        <v>555</v>
+      </c>
+      <c r="S155">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -9392,28 +9812,31 @@
         <v>347</v>
       </c>
       <c r="J156" s="1">
-        <v>0.0963931099213047</v>
+        <v>0.09639228617063077</v>
       </c>
       <c r="K156" t="s">
         <v>347</v>
+      </c>
+      <c r="L156" s="1">
+        <v>0</v>
       </c>
       <c r="M156">
         <v>3</v>
       </c>
-      <c r="N156">
+      <c r="O156">
+        <v>6</v>
+      </c>
+      <c r="Q156">
         <v>47847.93</v>
       </c>
-      <c r="O156">
-        <v>47847.93</v>
-      </c>
-      <c r="P156" t="s">
-        <v>221</v>
-      </c>
-      <c r="R156">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18">
+      <c r="R156" t="s">
+        <v>555</v>
+      </c>
+      <c r="S156">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
       <c r="A157" t="s">
         <v>24</v>
       </c>
@@ -9436,25 +9859,28 @@
         <v>347</v>
       </c>
       <c r="J157" s="1">
-        <v>0.2226563020955781</v>
+        <v>0.2226543892594307</v>
       </c>
       <c r="K157" t="s">
         <v>347</v>
+      </c>
+      <c r="L157" s="1">
+        <v>0</v>
       </c>
       <c r="M157">
         <v>2</v>
       </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
+      <c r="Q157">
         <v>110522.865</v>
       </c>
-      <c r="P157" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18">
+      <c r="R157" t="s">
+        <v>555</v>
+      </c>
+      <c r="S157">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
       <c r="A158" t="s">
         <v>24</v>
       </c>
@@ -9483,28 +9909,31 @@
         <v>347</v>
       </c>
       <c r="J158" s="1">
-        <v>0.2009487224892537</v>
+        <v>0.2009469951604869</v>
       </c>
       <c r="K158" t="s">
         <v>347</v>
+      </c>
+      <c r="L158" s="1">
+        <v>0</v>
       </c>
       <c r="M158">
         <v>3</v>
       </c>
-      <c r="N158">
+      <c r="O158">
+        <v>6</v>
+      </c>
+      <c r="Q158">
         <v>99747.58500000001</v>
       </c>
-      <c r="O158">
-        <v>99747.58500000001</v>
-      </c>
-      <c r="P158" t="s">
-        <v>221</v>
-      </c>
-      <c r="R158">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:18">
+      <c r="R158" t="s">
+        <v>555</v>
+      </c>
+      <c r="S158">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
       <c r="A159" t="s">
         <v>24</v>
       </c>
@@ -9533,28 +9962,31 @@
         <v>347</v>
       </c>
       <c r="J159" s="1">
-        <v>0.0217075796063243</v>
+        <v>0.02170739409894376</v>
       </c>
       <c r="K159" t="s">
         <v>347</v>
+      </c>
+      <c r="L159" s="1">
+        <v>0</v>
       </c>
       <c r="M159">
         <v>3</v>
       </c>
-      <c r="N159">
+      <c r="O159">
+        <v>6</v>
+      </c>
+      <c r="Q159">
         <v>10775.28</v>
       </c>
-      <c r="O159">
-        <v>10775.28</v>
-      </c>
-      <c r="P159" t="s">
-        <v>221</v>
-      </c>
-      <c r="R159">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18">
+      <c r="R159" t="s">
+        <v>555</v>
+      </c>
+      <c r="S159">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
       <c r="A160" t="s">
         <v>24</v>
       </c>
@@ -9577,28 +10009,31 @@
         <v>526</v>
       </c>
       <c r="J160" s="1">
-        <v>0.0207242266208391</v>
+        <v>0.02072404951693973</v>
       </c>
       <c r="K160" t="s">
         <v>347</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
       </c>
       <c r="M160">
         <v>1</v>
       </c>
       <c r="N160">
-        <v>0</v>
-      </c>
-      <c r="O160">
-        <v>20574.32</v>
-      </c>
-      <c r="P160" t="s">
-        <v>557</v>
+        <v>6.03</v>
       </c>
       <c r="Q160">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18">
+        <v>10287.16</v>
+      </c>
+      <c r="R160" t="s">
+        <v>555</v>
+      </c>
+      <c r="S160">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19">
       <c r="A161" t="s">
         <v>24</v>
       </c>
@@ -9621,25 +10056,28 @@
         <v>347</v>
       </c>
       <c r="J161" s="1">
-        <v>0.0207242266208391</v>
+        <v>0.02072404951693973</v>
       </c>
       <c r="K161" t="s">
         <v>347</v>
+      </c>
+      <c r="L161" s="1">
+        <v>0</v>
       </c>
       <c r="M161">
         <v>2</v>
       </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
-      <c r="O161">
+      <c r="Q161">
         <v>10287.16</v>
       </c>
-      <c r="P161" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18">
+      <c r="R161" t="s">
+        <v>555</v>
+      </c>
+      <c r="S161">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19">
       <c r="A162" t="s">
         <v>24</v>
       </c>
@@ -9668,28 +10106,31 @@
         <v>347</v>
       </c>
       <c r="J162" s="1">
-        <v>0.0207242266208391</v>
+        <v>0.02072404951693973</v>
       </c>
       <c r="K162" t="s">
         <v>347</v>
+      </c>
+      <c r="L162" s="1">
+        <v>0</v>
       </c>
       <c r="M162">
         <v>3</v>
       </c>
-      <c r="N162">
+      <c r="O162">
+        <v>6</v>
+      </c>
+      <c r="Q162">
         <v>10287.16</v>
       </c>
-      <c r="O162">
-        <v>10287.16</v>
-      </c>
-      <c r="P162" t="s">
-        <v>241</v>
-      </c>
-      <c r="R162">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18">
+      <c r="R162" t="s">
+        <v>555</v>
+      </c>
+      <c r="S162">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19">
       <c r="A163" t="s">
         <v>24</v>
       </c>
@@ -9709,31 +10150,34 @@
         <v>347</v>
       </c>
       <c r="I163" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J163" s="1">
-        <v>0.0157458963667794</v>
+        <v>0.0157457618064073</v>
       </c>
       <c r="K163" t="s">
         <v>347</v>
+      </c>
+      <c r="L163" s="1">
+        <v>0</v>
       </c>
       <c r="M163">
         <v>1</v>
       </c>
       <c r="N163">
-        <v>0</v>
-      </c>
-      <c r="O163">
-        <v>15632</v>
-      </c>
-      <c r="P163" t="s">
-        <v>557</v>
+        <v>6.04</v>
       </c>
       <c r="Q163">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18">
+        <v>7816</v>
+      </c>
+      <c r="R163" t="s">
+        <v>555</v>
+      </c>
+      <c r="S163">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19">
       <c r="A164" t="s">
         <v>24</v>
       </c>
@@ -9756,25 +10200,28 @@
         <v>347</v>
       </c>
       <c r="J164" s="1">
-        <v>0.010072861032996</v>
+        <v>0.01007277495292176</v>
       </c>
       <c r="K164" t="s">
         <v>347</v>
+      </c>
+      <c r="L164" s="1">
+        <v>0</v>
       </c>
       <c r="M164">
         <v>2</v>
       </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
-      <c r="O164">
+      <c r="Q164">
         <v>5000</v>
       </c>
-      <c r="P164" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="165" spans="1:18">
+      <c r="R164" t="s">
+        <v>555</v>
+      </c>
+      <c r="S164">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19">
       <c r="A165" t="s">
         <v>24</v>
       </c>
@@ -9803,28 +10250,31 @@
         <v>347</v>
       </c>
       <c r="J165" s="1">
-        <v>0.010072861032996</v>
+        <v>0.01007277495292176</v>
       </c>
       <c r="K165" t="s">
         <v>347</v>
+      </c>
+      <c r="L165" s="1">
+        <v>0</v>
       </c>
       <c r="M165">
         <v>3</v>
       </c>
-      <c r="N165">
+      <c r="O165">
+        <v>6</v>
+      </c>
+      <c r="Q165">
         <v>5000</v>
       </c>
-      <c r="O165">
-        <v>5000</v>
-      </c>
-      <c r="P165" t="s">
-        <v>244</v>
-      </c>
-      <c r="R165">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="166" spans="1:18">
+      <c r="R165" t="s">
+        <v>555</v>
+      </c>
+      <c r="S165">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19">
       <c r="A166" t="s">
         <v>24</v>
       </c>
@@ -9847,25 +10297,28 @@
         <v>347</v>
       </c>
       <c r="J166" s="1">
-        <v>0.0056730353337833</v>
+        <v>0.005672986853485537</v>
       </c>
       <c r="K166" t="s">
         <v>347</v>
+      </c>
+      <c r="L166" s="1">
+        <v>0</v>
       </c>
       <c r="M166">
         <v>2</v>
       </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
-      <c r="O166">
+      <c r="Q166">
         <v>2816</v>
       </c>
-      <c r="P166" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18">
+      <c r="R166" t="s">
+        <v>555</v>
+      </c>
+      <c r="S166">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19">
       <c r="A167" t="s">
         <v>24</v>
       </c>
@@ -9894,28 +10347,31 @@
         <v>347</v>
       </c>
       <c r="J167" s="1">
-        <v>0.0056730353337833</v>
+        <v>0.005672986853485537</v>
       </c>
       <c r="K167" t="s">
         <v>347</v>
+      </c>
+      <c r="L167" s="1">
+        <v>0</v>
       </c>
       <c r="M167">
         <v>3</v>
       </c>
-      <c r="N167">
+      <c r="O167">
+        <v>6</v>
+      </c>
+      <c r="Q167">
         <v>2816</v>
       </c>
-      <c r="O167">
-        <v>2816</v>
-      </c>
-      <c r="P167" t="s">
-        <v>244</v>
-      </c>
-      <c r="R167">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18">
+      <c r="R167" t="s">
+        <v>555</v>
+      </c>
+      <c r="S167">
+        <v>992775.084</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19">
       <c r="A168" t="s">
         <v>24</v>
       </c>
@@ -9935,19 +10391,16 @@
         <v>347</v>
       </c>
       <c r="K168" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L168" s="1">
-        <v>1</v>
-      </c>
-      <c r="N168">
-        <v>0</v>
-      </c>
-      <c r="O168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="Q168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19">
       <c r="A169" t="s">
         <v>24</v>
       </c>
@@ -9967,19 +10420,16 @@
         <v>347</v>
       </c>
       <c r="K169" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L169" s="1">
-        <v>1</v>
-      </c>
-      <c r="N169">
-        <v>0</v>
-      </c>
-      <c r="O169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="Q169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
       <c r="A170" t="s">
         <v>24</v>
       </c>
@@ -9999,12 +10449,12 @@
         <v>347</v>
       </c>
       <c r="K170" t="s">
-        <v>551</v>
-      </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
-      <c r="O170">
+        <v>549</v>
+      </c>
+      <c r="L170" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q170">
         <v>0</v>
       </c>
     </row>
